--- a/workspaces/btc_daily_14days/ma/ma_cross_7_21.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_7_21.xlsx
@@ -575,46 +575,46 @@
         <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.506561679790032</v>
+        <v>3.495464057507775</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.106540989030968</v>
+        <v>-6.086663262877032</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.501096188665663</v>
+        <v>-2.493195120840141</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.371352552463513</v>
+        <v>-2.363877356170562</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.910941868361135</v>
+        <v>-2.901539143457796</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.613938774508341</v>
+        <v>-2.605275600536039</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.306376214002718</v>
+        <v>1.30265666311422</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8383561555181629</v>
+        <v>0.8367217656357724</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.78510694039992</v>
+        <v>4.771082008773512</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.083746663393029</v>
+        <v>-4.069161108847837</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.729781721288383</v>
+        <v>3.719142498682189</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2456473002076578</v>
+        <v>-0.2437231093991556</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6673276010992524</v>
+        <v>-0.6640192620857235</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.608724540962612</v>
+        <v>7.585447582573579</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.4695246427513</v>
+        <v>10.8392410094879</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.450867824987441</v>
+        <v>1.497141512578381</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.761747327961785</v>
+        <v>4.930791119274993</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.893285693759495</v>
+        <v>5.067128995143321</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.77024135079373</v>
+        <v>12.18499578355701</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12.070881755644</v>
+        <v>12.49398923678046</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.570511329500306</v>
+        <v>4.727338475712976</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.813430961494795</v>
+        <v>8.078337211920051</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>22.59831333005553</v>
+        <v>23.38439124905147</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>29.17549256717345</v>
+        <v>30.18977474173572</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>21.55183362246322</v>
+        <v>22.30057270117325</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>17.87781299414819</v>
+        <v>18.49749885541767</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21.17537051798201</v>
+        <v>21.91122482579812</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>16.1030416807737</v>
+        <v>16.66237065950023</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6315616797900248</v>
+        <v>0.6516818539296168</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.106071145758897</v>
+        <v>-4.230819053762254</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-7.628667583562617</v>
+        <v>-7.851669709129993</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.372864114307042</v>
+        <v>-4.499927046334811</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.471452682203392</v>
+        <v>4.603990001589906</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.641406473969511</v>
+        <v>1.688828452989071</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.702549929711118</v>
+        <v>-4.84406402291058</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.088900376235237</v>
+        <v>1.11286366946026</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.42185026536274</v>
+        <v>10.72179246007233</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.83625924934056</v>
+        <v>16.29306898169288</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>18.76787434018583</v>
+        <v>19.31289369207425</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.406163246393959</v>
+        <v>9.675784619343034</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.90134189153651</v>
+        <v>14.30346818578298</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.00892709193079</v>
+        <v>11.32738306644636</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.142086968857392</v>
+        <v>-1.154143097048312</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.355767942753893</v>
+        <v>5.413450245774307</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.666178028632878</v>
+        <v>7.751287332770922</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.150888181730153</v>
+        <v>9.252851365682965</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.556119781587832</v>
+        <v>4.607548351712396</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5572831835780931</v>
+        <v>-0.5636651424167027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.349326564915309</v>
+        <v>-3.388187329200619</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.596600088280077</v>
+        <v>1.611373284282948</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.244280988582119</v>
+        <v>4.28985155765259</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.810973362986601</v>
+        <v>8.906873776273613</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.898530236737273</v>
+        <v>5.963054499867731</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>13.47109193136612</v>
+        <v>13.61899455987353</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.280971426416301</v>
+        <v>6.349424880435471</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.882462265306117</v>
+        <v>7.969009226411018</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>65</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.339592166364518</v>
+        <v>-6.323281996734828</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.279916540397195</v>
+        <v>1.276785650841703</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.042294653280202</v>
+        <v>7.023725880332769</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.095239826781757</v>
+        <v>4.084143585425892</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.017278443914918</v>
+        <v>2.011652836230503</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.305933953447848</v>
+        <v>-2.299895000207897</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.391690599469065</v>
+        <v>-2.384953257187192</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.84581474660385</v>
+        <v>4.833902393493297</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1612837099796778</v>
+        <v>0.1610435698292463</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.232749876437431</v>
+        <v>-2.226911264428544</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8960695730504113</v>
+        <v>-0.893786911486032</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.681031812929298</v>
+        <v>0.6790577843216354</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.801906429261777</v>
+        <v>1.797264711838274</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.574937923006473</v>
+        <v>-2.568398571271459</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4526219936791307</v>
+        <v>-0.4567375368435691</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.044077902203433</v>
+        <v>-1.052713812022326</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.481186661541834</v>
+        <v>-3.506669700950255</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.457786963380336</v>
+        <v>-8.522471844139218</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.870075787071478</v>
+        <v>-2.891210685785637</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.551530863015699</v>
+        <v>-1.564307091786716</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.769350059951499</v>
+        <v>-7.832704247513469</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.28398746536698</v>
+        <v>-10.36648408771925</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-14.43800966678931</v>
+        <v>-14.55252383212832</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-16.3168710735548</v>
+        <v>-16.44617360841836</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-11.85490660299548</v>
+        <v>-11.94850538888586</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-15.91294998202077</v>
+        <v>-16.03783357174615</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-11.21508007020521</v>
+        <v>-11.30344900743285</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.898630187946544</v>
+        <v>-7.960944170000985</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.846740606749826</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3395035799805015</v>
+        <v>0.3418640194089662</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.725669939669046</v>
+        <v>-6.784907476805387</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.18693855142552</v>
+        <v>1.198125993249462</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.872989500839587</v>
+        <v>2.900062187068762</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.621834359964275</v>
+        <v>7.689715560428105</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.764283566591764</v>
+        <v>9.848311597238443</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.072332908847912</v>
+        <v>7.132281287277131</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.672390141232043</v>
+        <v>3.701555893447242</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.223075159246569</v>
+        <v>1.2297218147325</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.018560171890542</v>
+        <v>1.024968490415944</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.28789842466518</v>
+        <v>-2.31143486909307</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.591281845836157</v>
+        <v>-1.608093974419482</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.457955029411195</v>
+        <v>-2.481968147762196</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.434614790798378</v>
+        <v>-5.464390078913361</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-6.312697833191194</v>
+        <v>-6.347272498614693</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-7.445258463911799</v>
+        <v>-7.485529215742488</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.373264528297234</v>
+        <v>-4.396505542360032</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9756289066845341</v>
+        <v>0.9819775953509691</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9353512999739593</v>
+        <v>-0.940010097527221</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.494086328402808</v>
+        <v>-2.508873647761114</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.963044311799557</v>
+        <v>-2.9805790775821</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.351543606010019</v>
+        <v>-3.371671934903894</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.459778326242223</v>
+        <v>-3.481056379190903</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.348139657083301</v>
+        <v>-7.389513407212533</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.419455055533753</v>
+        <v>-1.429204323941171</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.83780071121241</v>
+        <v>-1.849458934886407</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.010200467860891</v>
+        <v>-6.044182047054235</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>161</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.425115338843518</v>
+        <v>-3.417450269235715</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6891606754142288</v>
+        <v>-0.6870760014722777</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.084537352281139</v>
+        <v>-1.081717119364164</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.9543997455408615</v>
+        <v>-0.9522500299062671</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.115235454230792</v>
+        <v>-2.111354325413494</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5741270965374028</v>
+        <v>-0.5730247466694678</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.770965781101296</v>
+        <v>-3.762446433501211</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.995643931500879</v>
+        <v>-2.988610857095352</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.679403768861</v>
+        <v>-3.670728755700146</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.286711918486439</v>
+        <v>-3.278617915883217</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.491817790667554</v>
+        <v>-3.483371240200945</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.701896892086864</v>
+        <v>-4.691224107700222</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.990137566678222</v>
+        <v>-6.97483275591221</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-7.984937251143762</v>
+        <v>-7.967347448480503</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.372362087026218</v>
+        <v>-1.377093917694353</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.536424570876832</v>
+        <v>-2.543953417916889</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.176023032251102</v>
+        <v>-5.19034040696279</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.047197143751355</v>
+        <v>-5.060638050898241</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.995586502441341</v>
+        <v>-2.000368961256257</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.59675718228219</v>
+        <v>-2.603452036879602</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4614658283119937</v>
+        <v>0.4612688202484989</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.654864257874209</v>
+        <v>-0.6580193960691076</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.613896171766108</v>
+        <v>-1.61992018315231</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.910849932630221</v>
+        <v>-2.920495818630684</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.013712036868881</v>
+        <v>-4.026150043849064</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.530351241774092</v>
+        <v>-3.541316436053179</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.398662463933931</v>
+        <v>-4.412021497448428</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.453463508727062</v>
+        <v>-1.459597462469645</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-6.064866891638459</v>
+        <v>-6.079854160582641</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.900546560670286</v>
+        <v>-4.912885297090561</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.517991646781191</v>
+        <v>-2.525320844848153</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.785718968190487</v>
+        <v>-2.793126898406378</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9410603165108427</v>
+        <v>-0.9431326121266821</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5487830303924284</v>
+        <v>0.5496471537100547</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.080339437885208</v>
+        <v>1.081551928486768</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.806971405885321</v>
+        <v>1.809587653211253</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.746614481268317</v>
+        <v>1.748587767028951</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8988468219802854</v>
+        <v>0.8984625820009242</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.477233720905453</v>
+        <v>3.48255387919739</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.06632865357041595</v>
+        <v>-0.06872033397520738</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7071606620922211</v>
+        <v>0.7062441785858695</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.428819854497895</v>
+        <v>-1.434472736149708</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.129661983741393</v>
+        <v>3.132602973401319</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.471175119724421</v>
+        <v>5.477773230853551</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.46936883440749</v>
+        <v>4.474520226045492</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6454088662656261</v>
+        <v>0.6452026219008147</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.238195958391429</v>
+        <v>2.241446652028642</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.224756385552745</v>
+        <v>4.23085663011431</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.922993085325203</v>
+        <v>2.926610717720159</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.847731308856694</v>
+        <v>1.849671221377605</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.178344988194048</v>
+        <v>1.178915237634328</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.852035414706414</v>
+        <v>1.853180296508917</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.647333433187747</v>
+        <v>1.64842697219126</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.377497701893581</v>
+        <v>1.377932080756281</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.871234669639001</v>
+        <v>1.8723116161527</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.338499012859742</v>
+        <v>3.341545143551002</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.667351363688233</v>
+        <v>-4.694814569882027</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-6.281956927136058</v>
+        <v>-6.315281863937386</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.680298004208353</v>
+        <v>-6.716043324932585</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-9.001111580009479</v>
+        <v>-9.049426554087106</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-9.962078353256288</v>
+        <v>-10.01008953856202</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-9.086695097668617</v>
+        <v>-9.129557221837615</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.137378904244059</v>
+        <v>-7.173474612579419</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-8.18154978207177</v>
+        <v>-8.223748390369529</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.079990160729196</v>
+        <v>-7.118567518534334</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.764312786224401</v>
+        <v>-6.802511945544708</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.098529546195834</v>
+        <v>-6.132629701349231</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.322500956862463</v>
+        <v>-4.348975406977566</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.160426591336531</v>
+        <v>-4.186139638913723</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.232962757632507</v>
+        <v>-6.268779822672414</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.63121541940221</v>
+        <v>2.636031932235134</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.727759057133589</v>
+        <v>1.728886876014833</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.044129863668111</v>
+        <v>2.046080363014696</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.177118266843593</v>
+        <v>2.176333495622124</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8571130110402549</v>
+        <v>-0.8690515077507541</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.225202188270693</v>
+        <v>-2.242918762235767</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.584457606184806</v>
+        <v>-2.606204011541287</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.661874895466042</v>
+        <v>-1.680629750155724</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8901092241754256</v>
+        <v>-0.9059750402378057</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3492249948994228</v>
+        <v>-0.3633425650986695</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2765492896095338</v>
+        <v>0.267558706684099</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.141708716742194</v>
+        <v>1.137596460129807</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.277708674942488</v>
+        <v>1.274444913251827</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6966537374314825</v>
+        <v>0.6885116494277668</v>
       </c>
     </row>
     <row r="20">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.122</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.0389815476637736</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1124</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4049~4062</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4049</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.01763996634836928</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.1028</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4023~4035</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4023</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.05229829542682296</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.09312</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3992~4003</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3992</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.05776507514377016</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.08349</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3919~3929</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3919</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.03734262155892765</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.07385</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3854~3864</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3854</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.06867348103226334</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.06422</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3757~3766</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3757</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.08223879078311569</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.05458</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3668~3676</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3668</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.06368899208599288</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.04494</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3533~3540</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3533</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.2749232617109314</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.03531</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3372~3379</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3372</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.4512198626843684</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.02567</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3150~3156</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3150</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.5800724529205752</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.01604</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2899~2904</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2899</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.156699420836858</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.006402</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2571~2575</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2571</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.9046199322172086</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.003234</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2228~2230</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2228</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.766651365888677</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.01287</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1869~1869</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1869</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.599659593112655</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.02251</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1505~1505</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1505</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.725830782780058</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.03214</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1219~1219</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1219</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.305577266336378</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.04178</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1009~1009</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1009</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3.205273275429278</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.05141</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>856~856</t>
-        </is>
+      <c r="B24" t="n">
+        <v>856</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>4.515907474182541</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.06105</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>715~715</t>
-        </is>
+      <c r="B25" t="n">
+        <v>715</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>4.709358882587232</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.07068</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>606~606</t>
-        </is>
+      <c r="B26" t="n">
+        <v>606</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.942205244146457</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.08032</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>499~499</t>
-        </is>
+      <c r="B27" t="n">
+        <v>499</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.420389335100644</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.08996</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>417~417</t>
-        </is>
+      <c r="B28" t="n">
+        <v>417</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>5.54013482127683</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.09959</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>341~341</t>
-        </is>
+      <c r="B29" t="n">
+        <v>341</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>4.98456754489267</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.1092</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>284~284</t>
-        </is>
+      <c r="B30" t="n">
+        <v>284</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>4.900927876973128</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1189</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>226~226</t>
-        </is>
+      <c r="B31" t="n">
+        <v>226</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>5.471163449701528</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.1285</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>167~167</t>
-        </is>
+      <c r="B32" t="n">
+        <v>167</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.7999748534427198</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.1381</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>128~128</t>
-        </is>
+      <c r="B33" t="n">
+        <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-3.274688320209975</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.1478</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>104~104</t>
-        </is>
+      <c r="B34" t="n">
+        <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.1574</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.122</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-1.302962129733785</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1124</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>109~109</t>
-        </is>
+      <c r="B7" t="n">
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1998603385586009</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.1028</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>135~136</t>
-        </is>
+      <c r="B8" t="n">
+        <v>135</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.918326385672373</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.09312</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>166~168</t>
-        </is>
+      <c r="B9" t="n">
+        <v>166</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1.673228346456689</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.08349</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>239~242</t>
-        </is>
+      <c r="B10" t="n">
+        <v>239</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.8123468037569666</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.07385</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>304~307</t>
-        </is>
+      <c r="B11" t="n">
+        <v>304</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.7019073755845682</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.06422</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>401~405</t>
-        </is>
+      <c r="B12" t="n">
+        <v>401</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.6415864683581276</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.05458</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>490~495</t>
-        </is>
+      <c r="B13" t="n">
+        <v>490</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.3722261989978506</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.04494</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>625~631</t>
-        </is>
+      <c r="B14" t="n">
+        <v>625</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.463327385186197</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.03531</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>786~792</t>
-        </is>
+      <c r="B15" t="n">
+        <v>786</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.862125188896847</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.02567</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1008~1015</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1008</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.754522064052338</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.01604</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1259~1267</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1259</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-2.6118282176054</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.006402</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1587~1596</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1587</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.428275412941808</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.003234</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1930~1941</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1930</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-2.00399988641297</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.01287</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2289~2302</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2289</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.277104697273401</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.02251</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2653~2666</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2653</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.9555538490921975</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.03214</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2939~2952</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2939</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.9351727375541472</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.04178</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3149~3162</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3149</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.00703730819226</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.05141</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3302~3315</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3302</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.151055213120991</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.06105</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3443~3456</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3443</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.9598735053951586</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.07068</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3552~3565</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3552</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.6561311673347987</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.08032</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3659~3672</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3659</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.5871202374213027</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.08996</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3741~3754</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3741</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.6021223905349657</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.09959</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3817~3830</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3817</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.4307751348313857</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.1092</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3874~3887</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3874</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.3452520583113454</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1189</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3932~3945</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3932</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.300789397523026</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.1285</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3991~4004</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3991</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.02091084768250084</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.1381</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4030~4043</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4030</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1160101091741481</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.1478</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4054~4067</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4054</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.07602319933760526</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.1574</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.06344937247413895</v>

--- a/workspaces/btc_daily_14days/ma/ma_cross_7_21.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_7_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-7-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-7-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.495464057507775</v>
+        <v>3.507947962359694</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.086663262877032</v>
+        <v>-6.073797154750594</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.493195120840141</v>
+        <v>-2.48022574335161</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.363877356170562</v>
+        <v>-2.350932390789474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.901539143457796</v>
+        <v>-2.888459768312998</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.605275600536039</v>
+        <v>-2.592260430777003</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.30265666311422</v>
+        <v>1.315700231080719</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8367217656357724</v>
+        <v>0.8498828466997495</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.771082008773512</v>
+        <v>4.784265266747838</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.069161108847837</v>
+        <v>-4.055770766593895</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.719142498682189</v>
+        <v>3.732590109557108</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2437231093991556</v>
+        <v>-0.2302777459900724</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6640192620857235</v>
+        <v>-0.6504667324736459</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.585447582573579</v>
+        <v>7.575017946877246</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.8392410094879</v>
+        <v>10.44833966890795</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.497141512578381</v>
+        <v>1.459524247576162</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.930791119274993</v>
+        <v>4.759324500520478</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.067128995143321</v>
+        <v>4.89040091708285</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.18499578355701</v>
+        <v>11.74555235067832</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12.49398923678046</v>
+        <v>12.04536690233682</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.727338475712976</v>
+        <v>4.569272110210193</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.078337211920051</v>
+        <v>7.802466549448816</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>23.38439124905147</v>
+        <v>22.53990545948547</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>30.18977474173572</v>
+        <v>29.0965094916707</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>22.30057270117325</v>
+        <v>21.49708882436887</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.49749885541767</v>
+        <v>17.8348191567237</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21.91122482579812</v>
+        <v>21.12190231585905</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>16.66237065950023</v>
+        <v>17.64909202095132</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>31</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6516818539296168</v>
+        <v>0.6644072672884889</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.230819053762254</v>
+        <v>-4.216423380798034</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-7.851669709129993</v>
+        <v>-7.836312307913232</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.499927046334811</v>
+        <v>-4.485433566061644</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.603990001589906</v>
+        <v>4.616352404719983</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.688828452989071</v>
+        <v>1.701869201815356</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.84406402291058</v>
+        <v>-4.829341697808097</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.11286366946026</v>
+        <v>1.126260996562017</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.72179246007233</v>
+        <v>10.73279477061175</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>16.29306898169288</v>
+        <v>16.30291410933519</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>19.31289369207425</v>
+        <v>19.32202205460639</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.675784619343034</v>
+        <v>9.68732341906486</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>14.30346818578298</v>
+        <v>12.48206623816361</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.32738306644636</v>
+        <v>11.31695343074821</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>73</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.154143097048312</v>
+        <v>-1.141199593045364</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.413450245774307</v>
+        <v>5.425175704054446</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.751287332770922</v>
+        <v>7.762479000616239</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.252851365682965</v>
+        <v>9.263627327532618</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.607548351712396</v>
+        <v>4.619630920721249</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5636651424167027</v>
+        <v>-0.5503084219729146</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.388187329200619</v>
+        <v>-3.37405028087322</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.611373284282948</v>
+        <v>1.624387473364784</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.28985155765259</v>
+        <v>4.302172717475038</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.906873776273613</v>
+        <v>8.918240321121147</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.963054499867731</v>
+        <v>5.975204605582505</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>13.61899455987353</v>
+        <v>12.85986194830613</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.349424880435471</v>
+        <v>6.362980926787074</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.969009226411018</v>
+        <v>7.958579590712866</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>65</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.323281996734828</v>
+        <v>-6.309171320073673</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.276785650841703</v>
+        <v>1.289347497120346</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.023725880332769</v>
+        <v>7.034848214047095</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.084143585425892</v>
+        <v>4.0959868240936</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.011652836230503</v>
+        <v>2.024176815823907</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.299895000207897</v>
+        <v>-2.286270785433999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.384953257187192</v>
+        <v>-2.371232271423459</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.833902393493297</v>
+        <v>4.845878759506284</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1610435698292463</v>
+        <v>0.1742073479979638</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.226911264428544</v>
+        <v>-2.212929998944503</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.893786911486032</v>
+        <v>-0.8801051340883532</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.6790577843216354</v>
+        <v>0.6925100730417455</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.797264711838274</v>
+        <v>1.810820758189877</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.568398571271459</v>
+        <v>-2.578828206969611</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>97</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4567375368435691</v>
+        <v>-0.4439720425968332</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.052713812022326</v>
+        <v>-1.039400602624823</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.506669700950255</v>
+        <v>-3.492683857820758</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.522471844139218</v>
+        <v>-8.507180653084582</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.891210685785637</v>
+        <v>-2.877259583988412</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.564307091786716</v>
+        <v>-1.550703617279417</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.832704247513469</v>
+        <v>-7.817355970918705</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.36648408771925</v>
+        <v>-10.35036574571234</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-14.55252383212832</v>
+        <v>-14.53529582673414</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-16.44617360841836</v>
+        <v>-16.42822970779474</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-11.94850538888586</v>
+        <v>-12.51509542960492</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-16.03783357174615</v>
+        <v>-16.02438128302604</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-11.30344900743285</v>
+        <v>-11.28989296108124</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.960944170000985</v>
+        <v>-7.971373805699137</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>89</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.846740606749826</v>
+        <v>0.8591772556433952</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3418640194089662</v>
+        <v>0.3548321122972382</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.784907476805387</v>
+        <v>-6.769965858055926</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.198125993249462</v>
+        <v>1.210903387150744</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.900062187068762</v>
+        <v>2.91249338409748</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.689715560428105</v>
+        <v>7.700841367705664</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.848311597238443</v>
+        <v>9.858974247321456</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.132281287277131</v>
+        <v>7.143796069391044</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.701555893447242</v>
+        <v>3.714029192129495</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.2297218147325</v>
+        <v>0.6077782331153401</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.024968490415944</v>
+        <v>1.038425784126161</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.31143486909307</v>
+        <v>-2.29798258037296</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.608093974419482</v>
+        <v>-1.594537928067879</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.481968147762196</v>
+        <v>-2.492397783460348</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>135</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.464390078913361</v>
+        <v>-5.450233280086408</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-6.347272498614693</v>
+        <v>-6.332469563574421</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-7.485529215742488</v>
+        <v>-7.470324926239485</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.396505542360032</v>
+        <v>-4.382218388303919</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9819775953509691</v>
+        <v>0.9948485191376051</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.940010097527221</v>
+        <v>-0.9266252690296497</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.508873647761114</v>
+        <v>-2.494928442305962</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.9805790775821</v>
+        <v>-2.966369285912251</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.371671934903894</v>
+        <v>-3.770130424177715</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.481056379190903</v>
+        <v>-3.467651251538072</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.389513407212533</v>
+        <v>-7.376056113502315</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.429204323941171</v>
+        <v>-1.415752035221061</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.849458934886407</v>
+        <v>-1.835902888534804</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.044182047054235</v>
+        <v>-6.054611682752387</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>161</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.417450269235715</v>
+        <v>-3.403870832615716</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6870760014722777</v>
+        <v>-0.6739008462936056</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.081717119364164</v>
+        <v>-1.068335305184824</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.9522500299062671</v>
+        <v>-0.9389870277680856</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.111354325413494</v>
+        <v>-2.097708043258159</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5730247466694678</v>
+        <v>-0.5598382294002562</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.762446433501211</v>
+        <v>-3.748173079843049</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.988610857095352</v>
+        <v>-2.974430081915337</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.670728755700146</v>
+        <v>-3.657530016745383</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.278617915883217</v>
+        <v>-3.265212788230386</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.483371240200945</v>
+        <v>-3.469913946490728</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.691224107700222</v>
+        <v>-4.677771818980112</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.97483275591221</v>
+        <v>-6.961276709560607</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-7.967347448480503</v>
+        <v>-7.977777084178655</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>222</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.377093917694353</v>
+        <v>-1.363956827271259</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.543953417916889</v>
+        <v>-2.530080029960097</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.19034040696279</v>
+        <v>-5.175532571607285</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.060638050898241</v>
+        <v>-5.045960168343306</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.000368961256257</v>
+        <v>-1.986614530507993</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.603452036879602</v>
+        <v>-2.589525900999526</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4612688202484989</v>
+        <v>0.4744277529313976</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.6580193960691076</v>
+        <v>-0.8957712051539914</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.61992018315231</v>
+        <v>-1.606721444197547</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.920495818630684</v>
+        <v>-2.907090690977853</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.026150043849064</v>
+        <v>-4.012692750138847</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.541316436053179</v>
+        <v>-3.527864147333069</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.412021497448428</v>
+        <v>-4.398465451096826</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.459597462469645</v>
+        <v>-1.470027098167797</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>251</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-6.079854160582641</v>
+        <v>-6.065007180237139</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.912885297090561</v>
+        <v>-4.898048331121601</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.525320844848153</v>
+        <v>-2.511146280018451</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.793126898406378</v>
+        <v>-2.778962154757302</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9431326121266821</v>
+        <v>-0.9296470719138199</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5496471537100547</v>
+        <v>0.5626208585218464</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.081551928486768</v>
+        <v>0.8746159321894069</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.809587653211253</v>
+        <v>1.822768662506491</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.748587767028951</v>
+        <v>1.761786505983714</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8984625820009242</v>
+        <v>0.9118677096537553</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.48255387919739</v>
+        <v>3.496011172907608</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.06872033397520738</v>
+        <v>-0.05526804525509732</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7062441785858695</v>
+        <v>0.7198002249374724</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.434472736149708</v>
+        <v>-1.44490237184786</v>
       </c>
     </row>
     <row r="17">
@@ -1147,150 +1147,150 @@
         <v>328</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.132602973401319</v>
+        <v>3.144378569316331</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.477773230853551</v>
+        <v>5.488989819121471</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.474520226045492</v>
+        <v>4.486218718028262</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6452026219008147</v>
+        <v>0.6582787429636596</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.241446652028642</v>
+        <v>2.253758696662601</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.23085663011431</v>
+        <v>4.077057642472568</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.926610717720159</v>
+        <v>2.939676972020635</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.849671221377605</v>
+        <v>1.862852230672843</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.178915237634328</v>
+        <v>1.192113976589091</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.853180296508917</v>
+        <v>1.866585424161748</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.64842697219126</v>
+        <v>1.661884265901477</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.377932080756281</v>
+        <v>1.391384369476391</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.8723116161527</v>
+        <v>1.885867662504303</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.341545143551002</v>
+        <v>3.33111550785285</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001584</t>
+          <t>X ≈ -0.001583</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>343</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.694814569882027</v>
+        <v>-4.837669577445553</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-6.315281863937386</v>
+        <v>-6.299220680019928</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.716043324932585</v>
+        <v>-6.699651437339611</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-9.049426554087106</v>
+        <v>-9.197170993226628</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.01008953856202</v>
+        <v>-10.15635374835633</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-9.129557221837615</v>
+        <v>-9.11651432554325</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.173474612579419</v>
+        <v>-7.160408358278943</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-8.223748390369529</v>
+        <v>-8.210567381074291</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.118567518534334</v>
+        <v>-7.105368779579571</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.802511945544708</v>
+        <v>-6.789106817891877</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.132629701349231</v>
+        <v>-6.119172407639013</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.348975406977566</v>
+        <v>-4.335523118257456</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.186139638913723</v>
+        <v>-4.17258359256212</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.268779822672414</v>
+        <v>-6.279209458370566</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.008052</t>
+          <t>X ≈ 0.008053</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>359</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.636031932235134</v>
+        <v>2.648554221910757</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.728886876014833</v>
+        <v>1.586976532859133</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.046080363014696</v>
+        <v>1.902628760423404</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.176333495622124</v>
+        <v>2.189312638020589</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8690515077507541</v>
+        <v>-0.8559407033758148</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.242918762235767</v>
+        <v>-2.229875865941402</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.606204011541287</v>
+        <v>-2.593137757240811</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.680629750155724</v>
+        <v>-1.667448740860486</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9059750402378057</v>
+        <v>-0.8927763012830425</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3633425650986695</v>
+        <v>-0.3499374374458384</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.267558706684099</v>
+        <v>0.2810160003943167</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.137596460129807</v>
+        <v>1.151048748849917</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.274444913251827</v>
+        <v>1.28800095960343</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6885116494277668</v>
+        <v>0.6780820137296146</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>364</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.488394660232359</v>
+        <v>2.50130446980841</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.741877601987426</v>
+        <v>3.754884733405028</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.344658207122457</v>
+        <v>6.357637349520921</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.784258970072173</v>
+        <v>2.797369774447112</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.982799808886824</v>
+        <v>1.99584270518119</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.7991649927133224</v>
+        <v>0.8122312470137985</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.529783791734019</v>
+        <v>2.542964801029257</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.468783905551774</v>
+        <v>2.481982644506537</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.618658720523847</v>
+        <v>1.632063848176678</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.139180121480997</v>
+        <v>1.152637415191215</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6241127293758808</v>
+        <v>0.6375650180959909</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.169768255195393</v>
+        <v>-1.15621220884379</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4535794507072666</v>
+        <v>0.4431498150091144</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>286</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7451865719582287</v>
+        <v>-0.7326642822826059</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.597782737672922</v>
+        <v>-6.58477560625532</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.117879255415069</v>
+        <v>-6.104900113016605</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.159796973983788</v>
+        <v>-3.146686169608849</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.862355036268127</v>
+        <v>-2.849312139973762</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.345690152141799</v>
+        <v>-4.332623897841323</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.512174250224</v>
+        <v>-5.498993240928762</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.174572737804901</v>
+        <v>-4.161373998850138</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.276446174581039</v>
+        <v>-3.263041046928208</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.830849848548972</v>
+        <v>-3.817392554838754</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.796466691203541</v>
+        <v>-3.783014402483431</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.566371651798796</v>
+        <v>-4.552815605447194</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.666300669172855</v>
+        <v>-4.676730304871008</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>210</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.017247844019558</v>
+        <v>-2.004725554343935</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.485964314126562</v>
+        <v>-6.473054504550511</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.880833020723209</v>
+        <v>-6.867825889305607</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-9.131532269068032</v>
+        <v>-9.118553126669568</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.289001103187879</v>
+        <v>-7.275890298812939</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.56298773690073</v>
+        <v>-5.549944840606365</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.742959549411104</v>
+        <v>-3.729893295110628</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.3053810434307</v>
+        <v>-2.292200034135462</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.4616190248511032</v>
+        <v>-0.44842028589634</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3593632574981243</v>
+        <v>-0.3459581298452932</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.421259438958558</v>
+        <v>-3.40780214524834</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.386876281613183</v>
+        <v>-3.373423992893073</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9499880354151742</v>
+        <v>-0.9364319890635713</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.204495201623011</v>
+        <v>1.194065565924859</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>153</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.127425248314438</v>
+        <v>-4.114902958638815</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.817430233827899</v>
+        <v>-1.804520424251848</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.173083254149986</v>
+        <v>-4.160076122732384</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.428451036575161</v>
+        <v>-1.415471894176697</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.620467022889017</v>
+        <v>-2.607356218514077</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.59099894138258</v>
+        <v>-5.577956045088214</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.100569259962121</v>
+        <v>-1.087503005661645</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2605631162598812</v>
+        <v>-0.2473821069646434</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.282347316167673</v>
+        <v>-2.26914857721291</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.7890961262554512</v>
+        <v>0.8025012539082823</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.376441511787689</v>
+        <v>-1.362984218077472</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.03486881195852476</v>
+        <v>-0.0214165232384147</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.762312965387089</v>
+        <v>-1.748756919035486</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>141</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.534930474116223</v>
+        <v>3.547452763791846</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.214137002995983</v>
+        <v>1.227046812572034</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.783807303491713</v>
+        <v>5.796814434909315</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.949521429006893</v>
+        <v>0.9625005714053572</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.957199504714779</v>
+        <v>3.970310309089719</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7085421516503843</v>
+        <v>0.7215850479447496</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.042248150690241</v>
+        <v>2.055314404990717</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1566250355966048</v>
+        <v>0.1698060448918426</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.322814566897755</v>
+        <v>-1.309615827942991</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6639396806983484</v>
+        <v>0.6773448083511795</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4591863563808545</v>
+        <v>0.4726436500910722</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-4.470969493365921</v>
+        <v>-4.457517204645811</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6359049553746914</v>
+        <v>-0.6223489090230885</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.095403481254351</v>
+        <v>-1.105833116952503</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>109</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.974451588046904</v>
+        <v>8.986973877722527</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>11.03260274572485</v>
+        <v>11.0455125553009</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.968009268486</v>
+        <v>6.981016399903602</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.511106437790808</v>
+        <v>2.524085580189272</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.972685222718638</v>
+        <v>1.985796027093578</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.352695967773741</v>
+        <v>1.365738864068106</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.18539344316202</v>
+        <v>2.198459697462496</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.553072429701622</v>
+        <v>3.56625343899686</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.7397789655376599</v>
+        <v>0.7529777044924231</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.027777412150812</v>
+        <v>-1.014372284497981</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.519762841513213</v>
+        <v>1.533220135223431</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.554145998858687</v>
+        <v>1.567598287578797</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7009709974073175</v>
+        <v>-0.6874149510557146</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.135906298171676</v>
+        <v>4.125476662473524</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>107</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.712169156425531</v>
+        <v>1.724691446101154</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>10.38096937523698</v>
+        <v>10.39387918481303</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.11694179013567</v>
+        <v>8.129948921553272</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.378036044238598</v>
+        <v>6.391015186637063</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>9.577932586175777</v>
+        <v>9.591043390550716</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10.80995396314377</v>
+        <v>10.82299685943813</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.790640806619159</v>
+        <v>9.803707060919635</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>10.25803684708993</v>
+        <v>10.27121785638517</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.19703696090769</v>
+        <v>10.21023569986245</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.346911775879704</v>
+        <v>9.360316903532535</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.142158451562238</v>
+        <v>9.155615745272456</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.1111210481599</v>
+        <v>10.12457333688001</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>13.4291841942243</v>
+        <v>13.4427402405759</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>12.74432608724835</v>
+        <v>12.7338964515502</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>82</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.273926125087989</v>
+        <v>-1.261403835412366</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.96815879853309</v>
+        <v>12.98106860810914</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.256216921204853</v>
+        <v>5.269224052622455</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>11.48403102942196</v>
+        <v>11.49701017182043</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.067561033862034</v>
+        <v>6.080671838236974</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>13.68207614230937</v>
+        <v>13.69511903860374</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14.81685462015897</v>
+        <v>14.82992087445945</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.252110245767852</v>
+        <v>8.26529125506309</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.9715981644636</v>
+        <v>6.984796903418363</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.901960784313722</v>
+        <v>4.915365911966553</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.258183069752235</v>
+        <v>2.271640363462453</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.609639397829383</v>
+        <v>9.623091686549493</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.969872591762531</v>
+        <v>7.983428638114134</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.87813050940453</v>
+        <v>11.86770087370638</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>76</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>8.032877469263632</v>
+        <v>8.045399758939254</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.105514382615205</v>
+        <v>5.118424192191256</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.60538251812392</v>
+        <v>12.61838964954152</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>16.68300407178405</v>
+        <v>16.69598321418251</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>18.77616180408026</v>
+        <v>18.7892726084552</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.12623532074332</v>
+        <v>15.13927821703768</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20.30465949820796</v>
+        <v>20.31772575250844</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.94273925732113</v>
+        <v>11.95592026661637</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.51331831850717</v>
+        <v>14.52651705746193</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>14.97898260716353</v>
+        <v>14.99238773481636</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>17.40580823021433</v>
+        <v>17.41926552392455</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>18.75598086124401</v>
+        <v>18.76943314996412</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>17.01993677661489</v>
+        <v>17.03349282296649</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.90123705625967</v>
+        <v>19.89080742056152</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>57</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.401298521895292</v>
+        <v>5.413820811570915</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.789724908931035</v>
+        <v>3.802634718507086</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.65801409707128</v>
+        <v>8.671021228488883</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>19.31458301915246</v>
+        <v>19.32756216155092</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.249846014606611</v>
+        <v>8.26295681898155</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.547287952322272</v>
+        <v>8.560330848616637</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.953782305225431</v>
+        <v>4.966848559525907</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.995370836268492</v>
+        <v>8.00855184556373</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.425599020261629</v>
+        <v>4.438797759216392</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.821087870321428</v>
+        <v>1.834492997974259</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.616334546003792</v>
+        <v>1.629791839714009</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.739235022228883</v>
+        <v>4.752791068580486</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.234570389592939</v>
+        <v>3.224140753894787</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>58</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.678975472893519</v>
+        <v>2.691497762569142</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.10501193317419</v>
+        <v>-4.092102123598139</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.051604777701904</v>
+        <v>-1.038597646284302</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.093765438197806</v>
+        <v>-6.080786295799342</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-8.35632458430451</v>
+        <v>-8.34321377992957</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-8.058882646588849</v>
+        <v>-8.045839750294483</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-6.419478432826544</v>
+        <v>-6.406412178526068</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-10.33493769367706</v>
+        <v>-10.32175668438182</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-10.39593757985931</v>
+        <v>-10.38273884090454</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-9.521924833852758</v>
+        <v>-9.508519706199927</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.554264365066885</v>
+        <v>-4.540807071356667</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.795743276687027</v>
+        <v>-2.782290987966917</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.956415905471573</v>
+        <v>1.969971951823176</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4819993067133765</v>
+        <v>0.4715696710152244</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>59</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>18.69300235775613</v>
+        <v>18.70552464743175</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>22.16617450750373</v>
+        <v>22.17908431707978</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25.16113630938176</v>
+        <v>25.17414344079936</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>20.20664367927736</v>
+        <v>20.21962282167582</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21.36313771844253</v>
+        <v>21.37624852281747</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16.57583389344632</v>
+        <v>16.58887678974068</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>19.88093068464853</v>
+        <v>19.893996938949</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>24.49849304857893</v>
+        <v>24.51167405787417</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>26.13240841663389</v>
+        <v>26.14560715558865</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>23.58736797736866</v>
+        <v>23.60077310502149</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>21.68769939881378</v>
+        <v>21.70115669252399</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.94242153921013</v>
+        <v>14.95587382793024</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>21.30182794521436</v>
+        <v>21.31538399156597</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.687142497829598</v>
+        <v>9.676712862131446</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.869347041184746</v>
+        <v>4.882256850760797</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.474478334588156</v>
+        <v>4.487485466005758</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.604731467195656</v>
+        <v>4.61771060959412</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.502207688020917</v>
+        <v>1.515318492395856</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>21.76055302250332</v>
+        <v>21.77373403179856</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>21.69955313632097</v>
+        <v>21.71275187527573</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>28.54173564360077</v>
+        <v>28.5551407712536</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>25.77287975518063</v>
+        <v>25.78633704889084</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>25.80726291252603</v>
+        <v>25.82071520124614</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.8229057374786</v>
+        <v>22.8364617838302</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>23.07262706975489</v>
+        <v>23.06219743405673</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>24</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-6.660104986876647</v>
+        <v>-6.647582697201024</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.80465949820789</v>
+        <v>7.817725752508366</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>19.77647621324412</v>
+        <v>19.78967495219888</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>23.09301769488286</v>
+        <v>23.10642282253569</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.55493103723192</v>
+        <v>14.56838833094214</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.75598086124401</v>
+        <v>18.76943314996412</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>22.50239291696577</v>
+        <v>22.51594896331737</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>22.7521142492421</v>
+        <v>22.74168461354395</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.907897876401826</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5001193602291352</v>
+        <v>0.5131264916467373</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.304659498207855</v>
+        <v>5.317725752508331</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.77647621324405</v>
+        <v>14.78967495219881</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.92635102821613</v>
+        <v>18.93975615586896</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>23.72159770389858</v>
+        <v>23.7350549976088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>18.75598086124401</v>
+        <v>18.76943314996412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.33572625029911</v>
+        <v>13.34928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.58544758257537</v>
+        <v>8.575017946877217</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-7-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-7-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0389815476637736</v>
+        <v>0.03865344108990598</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1044839062775509</v>
+        <v>0.1041298313810231</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0323163802848967</v>
+        <v>-0.03263953870074232</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.03564121921034058</v>
+        <v>-0.0359629302483313</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0270480203557355</v>
+        <v>0.02670752778097807</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09296989357914498</v>
+        <v>0.09261490187984833</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1441596207268816</v>
+        <v>0.1437914065994903</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3276721778577638</v>
+        <v>0.3272559815469194</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4028552277084216</v>
+        <v>0.4024200502380708</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.4736781493539723</v>
+        <v>0.4732202402033892</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.40543385793341</v>
+        <v>0.4049912408653</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3555883195364586</v>
+        <v>0.355157947609456</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.366401096924875</v>
+        <v>0.365965319221857</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3355703120795681</v>
+        <v>0.3357541431962616</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4049</v>
+        <v>4050</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.01763996634836928</v>
+        <v>0.01723804281046171</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1427103027282541</v>
+        <v>0.1422651831472663</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.01712201908117095</v>
+        <v>-0.0175309818819116</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.02126584172847856</v>
+        <v>-0.02167299530673006</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04513018362947463</v>
+        <v>0.04470238763341428</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.109629843530449</v>
+        <v>0.109188206402429</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1370066382473425</v>
+        <v>0.136557401510089</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3245291203881635</v>
+        <v>0.3240298897867149</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3758842053506513</v>
+        <v>0.3753716229756705</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.5017272927115997</v>
+        <v>0.5011769748132409</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3849738144612616</v>
+        <v>0.3844505071079354</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3592886864723539</v>
+        <v>0.3587717481872303</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3727632873361486</v>
+        <v>0.372239591145906</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2908069305625602</v>
+        <v>0.2910673295932966</v>
       </c>
     </row>
     <row r="8">
@@ -2321,46 +2321,46 @@
         <v>4023</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05229829542682296</v>
+        <v>-0.05276935065327848</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.133956832319079</v>
+        <v>0.1334245182853309</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04909958348517307</v>
+        <v>-0.04959041464970682</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.05415131668713258</v>
+        <v>-0.05463993431605729</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.03332780931065571</v>
+        <v>-0.03382680674943828</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.02959172664641585</v>
+        <v>0.02907962455051916</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1073400641051308</v>
+        <v>0.106807638364451</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2744175095554837</v>
+        <v>0.2738390397218708</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2271839361147059</v>
+        <v>0.2266163623279454</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3098582313955021</v>
+        <v>0.3092619914786283</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.2427549479317008</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2420643602499837</v>
+        <v>0.2414828394051156</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2335636850492975</v>
+        <v>0.2329801097719866</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1850001552823315</v>
+        <v>0.1745705195841794</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3992</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.05776507514377016</v>
+        <v>-0.05833860795693369</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1678516350416572</v>
+        <v>0.1672033972611757</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.01149151718993835</v>
+        <v>0.01087761608455651</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.01962750716332096</v>
+        <v>-0.02023246873886819</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.06933904481613951</v>
+        <v>-0.0699379178605497</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.01670687230858192</v>
+        <v>0.01608952512786743</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1457903463439862</v>
+        <v>0.1451394593617863</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2679065298568233</v>
+        <v>0.267219530537993</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1456877276370818</v>
+        <v>0.145030307554201</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1857401118415964</v>
+        <v>0.1850627891606038</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09525159821363616</v>
+        <v>0.09459430657224743</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1688065125466096</v>
+        <v>0.1681308709758937</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1243034046077298</v>
+        <v>0.1378594509593327</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0984736346796069</v>
+        <v>0.08804399898145476</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3919</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.03734262155892765</v>
+        <v>-0.0381679389313021</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.07014081631660929</v>
+        <v>0.06926209121475324</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1326792137458668</v>
+        <v>-0.1335130195548473</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1923478331949084</v>
+        <v>-0.1931647895165725</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1564563655475979</v>
+        <v>-0.1572914583597864</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.02751757837516777</v>
+        <v>0.02663993343058024</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2116184581875018</v>
+        <v>0.2106921133646296</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2428815048317929</v>
+        <v>0.2419392907251918</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.06849355575875649</v>
+        <v>0.06759438106167437</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02328980372637091</v>
+        <v>0.02238813750632573</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.01404914478731456</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.08173284123110847</v>
+        <v>-0.0682805525109984</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.008346816770156806</v>
+        <v>0.02190286312175971</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.04813241232125876</v>
+        <v>-0.05856204801941089</v>
       </c>
     </row>
     <row r="11">
@@ -2477,98 +2477,98 @@
         <v>3854</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06867348103226334</v>
+        <v>0.06759625924572532</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.04979003420862682</v>
+        <v>0.04868462588422773</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2533762379065081</v>
+        <v>-0.2544116911127361</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2644734020092159</v>
+        <v>-0.2655038800419192</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1930228154997451</v>
+        <v>-0.1940832170058471</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06677077443326596</v>
+        <v>0.06564854700769729</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2554111830186727</v>
+        <v>0.2542378022621961</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1654512096156537</v>
+        <v>0.1642911159792746</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.06693264477936367</v>
+        <v>0.06579629002617082</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06124078178295633</v>
+        <v>0.06008810607646353</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.0007881553775561656</v>
+        <v>-0.0003535627024859878</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09456402718360124</v>
+        <v>-0.08111173846349118</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.02182434648345577</v>
+        <v>-0.008268300131852868</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.005626626039024529</v>
+        <v>-0.01605626173717667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06422</t>
+          <t>X &gt; -0.06421</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3757</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.08223879078311569</v>
+        <v>0.08080417121770722</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.07825499909667855</v>
+        <v>0.07677732409167248</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1693811711204489</v>
+        <v>-0.1708044512483085</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.05126449892520668</v>
+        <v>-0.05271637751724967</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1233597270201798</v>
+        <v>-0.1248077026067662</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1088827129542409</v>
+        <v>0.1073802904029222</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4642339662929942</v>
+        <v>0.4626340215857425</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.437369688146795</v>
+        <v>0.4357634917003494</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4443846751919338</v>
+        <v>0.4427741807170733</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4874370010668372</v>
+        <v>0.4857912809355227</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3093006583835489</v>
+        <v>0.3227579520937667</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3170668340946889</v>
+        <v>0.330519122814799</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2694499660297467</v>
+        <v>0.2830060123813496</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1997675186946353</v>
+        <v>0.1893378829964831</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3668</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.06368899208599288</v>
+        <v>0.06191780139385372</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.07185881512508985</v>
+        <v>0.07003062939420346</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.008862675698971145</v>
+        <v>-0.01068303216273847</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.08157958992944714</v>
+        <v>-0.08337672622376147</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1967197462006354</v>
+        <v>-0.1985044846996473</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.07505788776145295</v>
+        <v>-0.07686672046947507</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2365396071997168</v>
+        <v>0.2346421240692536</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2749249955833832</v>
+        <v>0.273000432972303</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3653529853269646</v>
+        <v>0.3634007630464922</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4694262735814902</v>
+        <v>0.4828314012343213</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2919357627862595</v>
+        <v>0.3053930564964773</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3808445471764017</v>
+        <v>0.3942968358965118</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3150065120221157</v>
+        <v>0.3285625583737186</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2648368955524987</v>
+        <v>0.2544072598543465</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3533</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2749232617109314</v>
+        <v>0.2725434441902976</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3171412174332886</v>
+        <v>0.3146775374187669</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2768293658820866</v>
+        <v>0.2743584780836201</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.08329870148807572</v>
+        <v>0.08088696593045341</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2417591294753194</v>
+        <v>-0.2441038777135276</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04200706740526527</v>
+        <v>-0.04439646741099068</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3414450103754092</v>
+        <v>0.3389421598633859</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.399321556544983</v>
+        <v>0.3967804816701275</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5081490125647719</v>
+        <v>0.5213477515195351</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6203787666820517</v>
+        <v>0.6337838943348828</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.58545278456657</v>
+        <v>0.5989100782767878</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4500085997099035</v>
+        <v>0.4634608884300135</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.397713230202875</v>
+        <v>0.4112692765544779</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5059117773107502</v>
+        <v>0.4954821416125981</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3372</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4512198626843684</v>
+        <v>0.4480780523058883</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3650887180987112</v>
+        <v>0.3618783439957838</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3416947229771736</v>
+        <v>0.3384669297758478</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1327421610831223</v>
+        <v>0.1295820172310016</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1524931666799318</v>
+        <v>-0.1556014249695536</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.01665302044158778</v>
+        <v>-0.01978611044768286</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5373900051749771</v>
+        <v>0.5340861555907637</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5610822678724148</v>
+        <v>0.5577427891248306</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7076743152606966</v>
+        <v>0.7208730542154598</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8065408265554268</v>
+        <v>0.8199459542082579</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7797234452983517</v>
+        <v>0.7931807390085694</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6954826406034513</v>
+        <v>0.7089349293235614</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7497238778198749</v>
+        <v>0.7632799241714778</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9104772385659103</v>
+        <v>0.9000476028677582</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>3150</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5800724529205752</v>
+        <v>0.5757833676284605</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.570106925779811</v>
+        <v>0.5656925532079029</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.731571484515797</v>
+        <v>0.7270726089209489</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4987518141180018</v>
+        <v>0.4943345141191031</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.02226192020503248</v>
+        <v>-0.02655859657922832</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1656547197645182</v>
+        <v>0.1613193605054946</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5427547363031309</v>
+        <v>0.5382906525400983</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6469999089501997</v>
+        <v>0.6601809182454375</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.8717143084821828</v>
+        <v>0.884913047436946</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.11842310072398</v>
+        <v>1.131880394434198</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.994076099339253</v>
+        <v>1.007528388059363</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.113504028076882</v>
+        <v>1.127060074428485</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.077511074638892</v>
+        <v>1.06708143894074</v>
       </c>
     </row>
     <row r="17">
@@ -2789,150 +2789,150 @@
         <v>2899</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.156699420836858</v>
+        <v>1.150753504749638</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.044833054769278</v>
+        <v>1.038751870892177</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.013558367810155</v>
+        <v>1.007442716242018</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7837678737398122</v>
+        <v>0.7777417110449321</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.05746851914382489</v>
+        <v>0.05163223036419851</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1324080481810981</v>
+        <v>0.1265740428090112</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4961048241823676</v>
+        <v>0.5091710784828436</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5463412253318722</v>
+        <v>0.55952223462711</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.7957932191081767</v>
+        <v>0.8089919580629399</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.083991593928481</v>
+        <v>1.097396721581312</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.91373292293963</v>
+        <v>0.9271902166498478</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.086094693600003</v>
+        <v>1.099546982320113</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.148765229257371</v>
+        <v>1.162321275608974</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.295002601547459</v>
+        <v>1.284572965849307</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.006402</t>
+          <t>X &gt; -0.0064</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2571</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9046199322172086</v>
+        <v>0.8964131620122302</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4792926511303577</v>
+        <v>0.471004672518319</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5720198654759727</v>
+        <v>0.5636315421518319</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8014455877044853</v>
+        <v>0.7929824164244152</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.221156462414406</v>
+        <v>-0.2293080578294493</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3904589821083206</v>
+        <v>-0.3774160858139552</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1860286152829502</v>
+        <v>0.1990948695834263</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3800665311650135</v>
+        <v>0.3932475404602513</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7469157309414811</v>
+        <v>0.7601144698962443</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.9858609465358796</v>
+        <v>0.9992660741887107</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8200029936690996</v>
+        <v>0.8334602873793173</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.048863008268519</v>
+        <v>1.062315296988629</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.056457483282394</v>
+        <v>1.070013529633997</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.033911215403094</v>
+        <v>1.023481579704942</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.003234</t>
+          <t>X &gt; 0.003235</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2228</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.766651365888677</v>
+        <v>1.7791736555643</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.525315567947345</v>
+        <v>1.513279042321109</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.694015230965263</v>
+        <v>1.681812000843728</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.317984701095206</v>
+        <v>2.33096384349367</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.285847148500594</v>
+        <v>1.298957952875533</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9549228384604191</v>
+        <v>0.9679657347547845</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.319022155299457</v>
+        <v>1.332088409599933</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.704621521329443</v>
+        <v>1.717802530624681</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.957804759025059</v>
+        <v>1.971003497979822</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.18487885586427</v>
+        <v>2.198283983517101</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.890358924724431</v>
+        <v>1.903816218434649</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.879858778658736</v>
+        <v>1.893311067378846</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.863553898414018</v>
+        <v>1.877109944765621</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.158158534101432</v>
+        <v>2.14772889840328</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1869</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.599659593112655</v>
+        <v>1.612181882788278</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.486213320972368</v>
+        <v>1.499123130548419</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.626390093241483</v>
+        <v>1.639397224659085</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.345193252601263</v>
+        <v>2.358172394999727</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.699762941755942</v>
+        <v>1.712873746130882</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.569168496379049</v>
+        <v>1.582211392673415</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.072984805859036</v>
+        <v>2.086051060159512</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.354865077489521</v>
+        <v>2.368046086784759</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.507883382853507</v>
+        <v>2.52108212180827</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.674344607670413</v>
+        <v>2.687749735323244</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.202068543919985</v>
+        <v>2.215525837630203</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.022433509719136</v>
+        <v>2.035885798439246</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.976710733980227</v>
+        <v>1.990266780331829</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.440450257802794</v>
+        <v>2.430020622104642</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1505</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.725830782780058</v>
+        <v>1.738353072455681</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.243825276128092</v>
+        <v>1.256735085704143</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.114737300428516</v>
+        <v>1.127744431846118</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.377880798484519</v>
+        <v>1.390859940882983</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.437466227930614</v>
+        <v>1.450577032305553</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.469127434749275</v>
+        <v>1.48217033104364</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.381071458340777</v>
+        <v>2.394137712641253</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.312559155904793</v>
+        <v>2.325740165200031</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.517340000619505</v>
+        <v>2.530538739574268</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.929673287352372</v>
+        <v>2.943078415005203</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.45913923213778</v>
+        <v>2.472596525847997</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.360632024034715</v>
+        <v>2.374084312754825</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.737719605780839</v>
+        <v>2.751275652132442</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.920995755332875</v>
+        <v>2.910566119634723</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1219</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.305577266336378</v>
+        <v>2.318099556012001</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.498761651731428</v>
+        <v>2.511671461307479</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.92423748984362</v>
+        <v>2.937244621261222</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.136525076921991</v>
+        <v>3.149504219320455</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.51606940737895</v>
+        <v>2.529180211753889</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.485373527211102</v>
+        <v>2.498416423505468</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.959294444885501</v>
+        <v>3.972360699185977</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.148386681871024</v>
+        <v>4.161567691166262</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.087386795688722</v>
+        <v>4.100585534643486</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.385743973253078</v>
+        <v>4.399149100905909</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.934887285522869</v>
+        <v>3.948344579233087</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.805201533926535</v>
+        <v>3.818653822646645</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.451394831103052</v>
+        <v>4.464950877454655</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.701116163379339</v>
+        <v>4.690686527681187</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1009</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.205273275429278</v>
+        <v>3.2177955651049</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.368724439471947</v>
+        <v>4.381634249047998</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.964936010377841</v>
+        <v>4.977943141795443</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.689837309486819</v>
+        <v>5.702816451885283</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.556767927913171</v>
+        <v>4.56987873228811</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.160453671377098</v>
+        <v>4.173496567671464</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.562340370358534</v>
+        <v>5.57540662465901</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.491589082578024</v>
+        <v>5.504770091873262</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.034157085394732</v>
+        <v>5.047355824349495</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.373328233369776</v>
+        <v>5.386733361022607</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.46589899230294</v>
+        <v>5.479356286013157</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.302066094147882</v>
+        <v>5.315518382867992</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.575567677454707</v>
+        <v>5.58912372380631</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.428856898730004</v>
+        <v>5.418427263031852</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>856</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.515907474182541</v>
+        <v>4.528429763858163</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.474427319162217</v>
+        <v>5.487337128738268</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.59825020135068</v>
+        <v>6.611257332768282</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.962148193771256</v>
+        <v>6.97512733616972</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.839614829166372</v>
+        <v>5.852725633541311</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.903411907068957</v>
+        <v>5.916454803363322</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.753257629049017</v>
+        <v>6.766323883349493</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.519719090080592</v>
+        <v>6.53290009937583</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.341896773991749</v>
+        <v>6.355095512946512</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.19270616840307</v>
+        <v>6.206111296055902</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.688887423524747</v>
+        <v>6.702344717234965</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.887128119457984</v>
+        <v>6.900684165809587</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.552737302201564</v>
+        <v>6.542307666503412</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>715</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.709358882587232</v>
+        <v>4.721881172262854</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.314568486406188</v>
+        <v>6.327478295982239</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.758860618970431</v>
+        <v>6.771867750388033</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8.147855010319191</v>
+        <v>8.160834152717655</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.210832396645628</v>
+        <v>6.223943201020568</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.927854753941709</v>
+        <v>6.940897650236074</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.68228187583027</v>
+        <v>7.695348130130746</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.77453903648933</v>
+        <v>7.787720045784567</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.853399290167161</v>
+        <v>7.866598029121924</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.282994384859521</v>
+        <v>7.296399512512352</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.917401899702782</v>
+        <v>7.930859193412999</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.371365476628625</v>
+        <v>8.384817765348735</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.370691285264137</v>
+        <v>8.38424733161574</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.060972058099864</v>
+        <v>8.050542422401712</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>606</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.942205244146457</v>
+        <v>3.95472753382208</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.465945162535341</v>
+        <v>5.478854972111392</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.721241472440404</v>
+        <v>6.734248603858006</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.161725628150208</v>
+        <v>9.174704770548672</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.973139396576386</v>
+        <v>6.986250200951325</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.930647340892705</v>
+        <v>7.94369023718707</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.670996131871256</v>
+        <v>8.684062386171732</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.533845736390091</v>
+        <v>8.547026745685329</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>9.132911856808441</v>
+        <v>9.146110595763204</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.777836176731014</v>
+        <v>8.791241304383846</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.068132357363936</v>
+        <v>9.081589651074154</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.597565019659854</v>
+        <v>9.611017308379964</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.766965734390581</v>
+        <v>8.756536098692429</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>499</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.420389335100644</v>
+        <v>4.432911624776267</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.412022134962044</v>
+        <v>4.424931944538095</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.421963047603931</v>
+        <v>6.434970179021533</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9.758629005862723</v>
+        <v>9.771608148261187</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.414596568345665</v>
+        <v>6.427707372720604</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.313240910870945</v>
+        <v>7.326283807165311</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.430912003217905</v>
+        <v>8.443978257518381</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.164129406039613</v>
+        <v>8.177310415334851</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.904732726270133</v>
+        <v>8.917931465224896</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.655809946051832</v>
+        <v>8.669215073704663</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.052259026543865</v>
+        <v>9.065716320254083</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.487443787095714</v>
+        <v>9.500896075815824</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.267589977754021</v>
+        <v>9.281146024105624</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.914104897204652</v>
+        <v>7.9036752615065</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>417</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.54013482127683</v>
+        <v>5.552657110952453</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.729520440926485</v>
+        <v>2.742430250502537</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.651198496919825</v>
+        <v>6.664205628337427</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.419341317776727</v>
+        <v>9.432320460175191</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.482838567932369</v>
+        <v>6.495949372307308</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.060856045216383</v>
+        <v>6.073898941510748</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.175163095330198</v>
+        <v>7.188229349630674</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.146828617411998</v>
+        <v>8.160009626707236</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.284869498615784</v>
+        <v>9.298068237570547</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.393976927496738</v>
+        <v>9.407382055149569</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.463414914001802</v>
+        <v>9.476867202721913</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.522776610011341</v>
+        <v>9.536332656362944</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.134608254038234</v>
+        <v>7.124178618340082</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>341</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.98456754489267</v>
+        <v>4.997089834568293</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.199973404069176</v>
+        <v>2.212883213645227</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.324166281050296</v>
+        <v>5.337173412467898</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.800460469376269</v>
+        <v>7.813439611774733</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.74297767072639</v>
+        <v>3.756088475101329</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.040419608442051</v>
+        <v>4.053462504736416</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.248941023134577</v>
+        <v>4.262007277435053</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.300819207930786</v>
+        <v>7.314000217226024</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.119584717642915</v>
+        <v>8.132783456597679</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.149224928509412</v>
+        <v>8.162630056162243</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.824237000086256</v>
+        <v>8.837694293796474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.392344497607645</v>
+        <v>7.405796786327755</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.851855282557175</v>
+        <v>7.865411328908777</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.28925989929094</v>
+        <v>4.278830263592788</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>284</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.900927876973128</v>
+        <v>4.913450166648751</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.880903559783519</v>
+        <v>1.89381336935957</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.655048937693962</v>
+        <v>4.668056069111564</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.489527422414142</v>
+        <v>5.502506564812606</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.838430151003948</v>
+        <v>2.851540955378887</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.135872088719609</v>
+        <v>3.148914985013974</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.107476399616338</v>
+        <v>4.120542653916814</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.161419761398214</v>
+        <v>7.174600770693452</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.860983255497608</v>
+        <v>8.874181994452371</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.41930877469504</v>
+        <v>9.432713902347871</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.27089347854647</v>
+        <v>10.28435077225669</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.488375227441196</v>
+        <v>7.501827516161306</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.476571320721654</v>
+        <v>8.490127367073256</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.500940540321871</v>
+        <v>4.490510904623719</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>226</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.471163449701528</v>
+        <v>5.483685739377151</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.417111960631075</v>
+        <v>3.430021770207127</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.119588386777856</v>
+        <v>6.132595518195458</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.462230899916321</v>
+        <v>8.475210042314785</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.711420304313187</v>
+        <v>5.724531108688126</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.008862242028847</v>
+        <v>6.021905138323213</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.809084276968946</v>
+        <v>6.822150531269422</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.65163539146179</v>
+        <v>11.66481640075703</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.80302488581045</v>
+        <v>13.81622362476521</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.28033332910111</v>
+        <v>14.29373845675394</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>14.07558000478353</v>
+        <v>14.08903729849375</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.12766227717321</v>
+        <v>10.14111456589333</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.14988554233451</v>
+        <v>10.16344158868611</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.53235023744265</v>
+        <v>5.521920601744498</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>167</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.7999748534427198</v>
+        <v>0.8124971431183425</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.206808340359856</v>
+        <v>-3.193898530783805</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6076650709085456</v>
+        <v>-0.5946579394909435</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.3130072233756</v>
+        <v>4.325986365774064</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1817716370459479</v>
+        <v>0.1948824414208872</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.275620760390353</v>
+        <v>2.288663656684719</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.190887043118074</v>
+        <v>2.203953297418551</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.112925201222801</v>
+        <v>7.126106210518039</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.447134895878811</v>
+        <v>9.460333634833574</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.99221929168921</v>
+        <v>11.00562441934204</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.38626836258122</v>
+        <v>11.39972565629144</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.426639543878736</v>
+        <v>8.440091832598846</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.209977747305096</v>
+        <v>6.223533793656699</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.064489498743065</v>
+        <v>4.054059863044913</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.274688320209975</v>
+        <v>-3.262166030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-5.667511933174232</v>
+        <v>-5.654602123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.156130639770822</v>
+        <v>-2.14312350835322</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.224122492836678</v>
+        <v>4.237101635235142</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2205487222354918</v>
+        <v>-0.2074379178605525</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7043567845198311</v>
+        <v>-0.6913138882254657</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.7734094982078901</v>
+        <v>0.7864757525083661</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.649976099426389</v>
+        <v>2.663157108721627</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.713976213244088</v>
+        <v>5.727174952198851</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.64510102821616</v>
+        <v>5.658506155868992</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.002847703898581</v>
+        <v>7.016304997608799</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.130980861244012</v>
+        <v>3.144433149964122</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.148226250299111</v>
+        <v>1.161782296650713</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.727052417424602</v>
+        <v>-1.737482053122754</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.028088856251152</v>
+        <v>-6.015179046675101</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.615265255155435</v>
+        <v>-1.602258123737833</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.284218646682831</v>
+        <v>4.297197789081295</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.984971799158565</v>
+        <v>-2.971860994783626</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.649068322981371</v>
+        <v>-3.636025426687006</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>-0.8361204013377872</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.6067068686571631</v>
+        <v>0.6198878779524009</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.468783905551774</v>
+        <v>2.481982644506537</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.618658720523847</v>
+        <v>1.632063848176678</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4747883695252142</v>
+        <v>-0.4613360808051041</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.779658365085503</v>
+        <v>-3.7661023187339</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.376090878963069</v>
+        <v>-7.386520514661221</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-7.676440504602802</v>
+        <v>-7.663530695026751</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.118928258818435</v>
+        <v>-2.105921127400833</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.801082974996021</v>
+        <v>-5.788040078701655</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.314388120839723</v>
+        <v>-2.301321866539247</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4006191386688442</v>
+        <v>-0.3874381293736064</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4616190248511458</v>
+        <v>-0.4484202858963826</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.488815272702439</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.053542948279798</v>
+        <v>-5.040090659559688</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.854749940177079</v>
+        <v>-7.841193893825476</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-11.17645717932936</v>
+        <v>-11.18688681502751</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-7-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-7-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.302962129733785</v>
+        <v>-1.290439840058163</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465507444027736</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1461439603307255</v>
+        <v>-0.1330331559557862</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.216611507273079</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.49585723390694</v>
+        <v>-13.4826762246117</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.93780950104163</v>
+        <v>-15.92461076208686</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-19.16888706702193</v>
+        <v>-19.1554819393691</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-15.80221181991094</v>
+        <v>-15.78875452620073</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.38687628161313</v>
+        <v>-13.37342399289302</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.80713089255804</v>
+        <v>-13.79357484620643</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-13.55740956028175</v>
+        <v>-13.5678391959799</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1998603385586009</v>
+        <v>-0.1873380488829781</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.728865144183402</v>
+        <v>-2.715955334607351</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5459909198622057</v>
+        <v>0.5589980512798078</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.59367524513025</v>
+        <v>1.606654387528714</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7796083552630151</v>
+        <v>-0.7664975508880758</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.317028802868457</v>
+        <v>-2.303985906574091</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.401762520140736</v>
+        <v>-2.38869626584026</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-10.20839546020664</v>
+        <v>-10.1952144509114</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.18682653904948</v>
+        <v>-11.17362780009472</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-15.70667649471962</v>
+        <v>-15.69327136706679</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.32427385573445</v>
+        <v>-11.31081656202423</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-10.37245950572846</v>
+        <v>-10.35900721700835</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.79271411667337</v>
+        <v>-10.77915807032176</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.708130399075976</v>
+        <v>-8.718560034774129</v>
       </c>
     </row>
     <row r="8">
@@ -4012,49 +4012,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.918326385672373</v>
+        <v>1.930848675347995</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.899129580233051</v>
+        <v>-1.886219770657</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.382472301405649</v>
+        <v>1.395479432823251</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.248019551660207</v>
+        <v>2.260998694058671</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.709598336588037</v>
+        <v>1.722709140962976</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5364520390095819</v>
+        <v>0.5494949353039473</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.01886991355682</v>
+        <v>-1.005803659256344</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.633112135867727</v>
+        <v>-6.619931126572489</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.488229669108854</v>
+        <v>-4.475030930154091</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.808943089430898</v>
+        <v>-6.795537961778066</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.807814060807303</v>
+        <v>-4.794356767097085</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.773430903461872</v>
+        <v>-4.759978614741762</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.458391396759708</v>
+        <v>-4.444835350408106</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.821959824832014</v>
+        <v>-3.483805582534515</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.31929764745994</v>
+        <v>-2.306387837883889</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9875153499795388</v>
+        <v>1.000494492378003</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7465360726230301</v>
+        <v>0.7595789689173955</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.719150025601635</v>
+        <v>-1.706083771301159</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.488815272702439</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3260213437204627</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.077352472089323</v>
+        <v>-2.063900183369213</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9756509952098753</v>
+        <v>-1.293574846206425</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.9928656704366503</v>
+        <v>-0.73635929863174</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8123468037569666</v>
+        <v>0.8248690934325893</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.0272194717844414</v>
+        <v>0.04012928136049254</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.111689608163061</v>
+        <v>2.124696739580664</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.481612162258159</v>
+        <v>3.494591304656623</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.94319094718599</v>
+        <v>2.956301751560929</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3480709014305745</v>
+        <v>0.3611137977249399</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.2160016588169</v>
+        <v>-2.202935404516424</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.096408198094267</v>
+        <v>-3.083227188799029</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1483770396903736</v>
+        <v>0.1615757786451368</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.95114441664591</v>
+        <v>0.9645495442987411</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.572837373320063</v>
+        <v>1.58629466703028</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.677142686970157</v>
+        <v>2.44711910037735</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.252392916965782</v>
+        <v>1.02563084436855</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.744443398474985</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
     <row r="11">
@@ -4168,101 +4168,101 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7019073755845682</v>
+        <v>-0.6893850859089454</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2923822036335864</v>
+        <v>0.3052920132096375</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.154842487265014</v>
+        <v>3.167849618682617</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.61082851889531</v>
+        <v>3.623807661293775</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.746674404800345</v>
+        <v>2.759785209175284</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2132126477120124</v>
+        <v>-0.200169751417647</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.252343759121096</v>
+        <v>-2.23927750482062</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.416595561811391</v>
+        <v>-1.403414552516153</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1510690471203091</v>
+        <v>0.1642677860750723</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2781425591607913</v>
+        <v>0.2915476868136224</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.050587931911615</v>
+        <v>1.064045225621832</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.252712887387808</v>
+        <v>2.075622075045558</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.368513135545015</v>
+        <v>1.192419551552682</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8222896878385484</v>
+        <v>0.9520671272051118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06422</t>
+          <t>X &lt; -0.06421</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6415864683581276</v>
+        <v>-0.6290641786825049</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.03093785910015612</v>
+        <v>-0.01802804952410497</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.549502076278557</v>
+        <v>1.562509207696159</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6921008878984054</v>
+        <v>0.7050800302968696</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.388247574060806</v>
+        <v>1.401358378435745</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5365327104457549</v>
+        <v>-0.5234898141513895</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.584229390681003</v>
+        <v>-3.571163136380527</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.557585628968674</v>
+        <v>-3.544404619673436</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.371671934904064</v>
+        <v>-3.358473195949301</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.727969959438155</v>
+        <v>-3.714564831785324</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.070481504022204</v>
+        <v>-2.190870928317125</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.149726334785768</v>
+        <v>-2.270170810431914</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.689149371591434</v>
+        <v>-1.812008025929934</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.302332966053029</v>
+        <v>-1.201101456107828</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3722261989978506</v>
+        <v>-0.3597039093222278</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.03640220823991314</v>
+        <v>0.04931201781596428</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7818876443518263</v>
+        <v>0.7948667867502905</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.657607843421069</v>
+        <v>1.670718647796008</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.159986966438574</v>
+        <v>-1.146920712138098</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.627170365220074</v>
+        <v>-1.613989355924836</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.092210655442784</v>
+        <v>-2.079011916488021</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.834782575022707</v>
+        <v>-2.928930712817881</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.511668016182561</v>
+        <v>-1.609074557047066</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.178978488349486</v>
+        <v>-2.275191596486181</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.674457049089895</v>
+        <v>-1.772668922861477</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.516593233751131</v>
+        <v>-1.43516535251176</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.463327385186197</v>
+        <v>-1.450805095510574</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.331636338879463</v>
+        <v>-1.318726529303412</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.568026440087777</v>
+        <v>-1.555019308670175</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3284230697623727</v>
+        <v>-0.3154439273639085</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.510334795989543</v>
+        <v>1.523445600364482</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5399478905990236</v>
+        <v>0.552990786893389</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.446529091332529</v>
+        <v>-1.433462837032053</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.91371249011403</v>
+        <v>-1.900531480818792</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.366380929613051</v>
+        <v>-2.436949453506379</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.973489989271911</v>
+        <v>-3.044370828257989</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.775217582725624</v>
+        <v>-2.846820996031902</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.01754385964913</v>
+        <v>-2.09043946150085</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.712197072384591</v>
+        <v>-1.78628389154705</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.4945524174246</v>
+        <v>-2.431371829480582</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.862125188896847</v>
+        <v>-1.849602899221225</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.200971529133824</v>
+        <v>-1.188061719557773</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.469577609467791</v>
+        <v>-1.456570478050189</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4554860930219107</v>
+        <v>-0.4425069506234465</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7737694595826881</v>
+        <v>0.7868802639576273</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.313635639722591</v>
+        <v>0.3266785360169564</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.917562724014331</v>
+        <v>-1.904496469713855</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.132220870270579</v>
+        <v>-2.119039860975342</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.631867655276778</v>
+        <v>-2.685072522548616</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.035674288239534</v>
+        <v>-3.089320961703699</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.919720420309275</v>
+        <v>-2.973805761884876</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.563816093070706</v>
+        <v>-2.618399549655649</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.788797256689456</v>
+        <v>-2.84361110436452</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.615570229129439</v>
+        <v>-3.566023984507765</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.754522064052338</v>
+        <v>-1.741999774376715</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.494174494750588</v>
+        <v>-1.481264685174537</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.283131871297911</v>
+        <v>-2.270124739880309</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.463223566276618</v>
+        <v>-1.450244423878154</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1658429033802733</v>
+        <v>0.1789537077552126</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.311849602511181</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.394847890954672</v>
+        <v>-1.381781636654196</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.809466701362574</v>
+        <v>-1.848850280440935</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.41009831785167</v>
+        <v>-2.448983824921463</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.010407865064465</v>
+        <v>-3.049385008987869</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.162675293134058</v>
+        <v>-3.201703895671827</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.778672604102518</v>
+        <v>-2.81810394202401</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.145938764567092</v>
+        <v>-3.185371168695816</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.140742893615077</v>
+        <v>-3.104863123489459</v>
       </c>
     </row>
     <row r="17">
@@ -4480,153 +4480,153 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.6118282176054</v>
+        <v>-2.599305927929777</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.171310275715669</v>
+        <v>-2.158400466139618</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.329399187521418</v>
+        <v>-2.316392056103815</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.725586465332221</v>
+        <v>-1.712607322933756</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.05406292902318199</v>
+        <v>-0.04095212464824272</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1512539826255974</v>
+        <v>-0.138211086331232</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9038713074793208</v>
+        <v>-0.9332608299699245</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.091377655514322</v>
+        <v>-1.120906872321022</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.584283280426803</v>
+        <v>-1.613487103137118</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.233585630532851</v>
+        <v>-2.26277548970063</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.841001345229792</v>
+        <v>-1.87064571498027</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.239261010286519</v>
+        <v>-2.268601715329062</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.378559463986605</v>
+        <v>-2.408053151406385</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.800573068735169</v>
+        <v>-2.774188402329102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.006402</t>
+          <t>X &lt; -0.0064</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.428275412941808</v>
+        <v>-1.415753123266185</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5962400033496706</v>
+        <v>-0.5833301937736195</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9284520683422528</v>
+        <v>-0.9154449369246507</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.236795426962821</v>
+        <v>-1.223816284564357</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4177658141053655</v>
+        <v>0.4308766184803048</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7498947828782931</v>
+        <v>0.7282506481153916</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1156667251296213</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4858132916596105</v>
+        <v>-0.5069338574013358</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.014981073188068</v>
+        <v>-1.035811551253758</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.391059405473349</v>
+        <v>-1.412002638100866</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.121169591698902</v>
+        <v>-1.142380577501193</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.492603153859832</v>
+        <v>-1.51358571796041</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.500545790003159</v>
+        <v>-1.521705746143496</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.53112456613286</v>
+        <v>-1.513143262190766</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.003234</t>
+          <t>X &lt; 0.003235</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.00399988641297</v>
+        <v>-2.017476277702222</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.606299929052646</v>
+        <v>-1.593390119476595</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.949648800512712</v>
+        <v>-1.93664166909511</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.617050187575686</v>
+        <v>-2.630733887691186</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.426872858388151</v>
+        <v>-1.441329670437874</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9986356802886576</v>
+        <v>-1.013242072856713</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.365448916866974</v>
+        <v>-1.379900666480282</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.856738776606669</v>
+        <v>-1.871077532476107</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.096908799675809</v>
+        <v>-2.111151494082144</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.350794783572873</v>
+        <v>-2.365153404854524</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.010425058646682</v>
+        <v>-2.025027732484276</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.999712720536529</v>
+        <v>-2.014322670004837</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.977582915936004</v>
+        <v>-1.992332610181585</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.373101640222529</v>
+        <v>-2.359730887923376</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.277104697273401</v>
+        <v>-1.286821371394097</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.084586031392398</v>
+        <v>-1.094708552790188</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.325967596292564</v>
+        <v>-1.336069510091598</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.868540077846227</v>
+        <v>-1.87838749519964</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.339728443732447</v>
+        <v>-1.349918344132853</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.193105696143689</v>
+        <v>-1.20330801355184</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.559452000049951</v>
+        <v>-1.569518479098072</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.83923836166165</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.91053337699131</v>
+        <v>-1.920564699217266</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.039632399607648</v>
+        <v>-2.049781769152801</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.653620446188675</v>
+        <v>-1.66398556061187</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.50809596110431</v>
+        <v>-1.518524965219122</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.467767199482552</v>
+        <v>-1.478303910245842</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.892927253597598</v>
+        <v>-1.883497336965547</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9555538490921975</v>
+        <v>-0.9623558505568539</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5965691564387754</v>
+        <v>-0.6037300305749298</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.633514273404451</v>
+        <v>-0.6407196621993734</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7458948747938194</v>
+        <v>-0.7530447611612558</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7758173172768181</v>
+        <v>-0.7830340500423105</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.7586714218742117</v>
+        <v>-0.7658584036274192</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.236693885250759</v>
+        <v>-1.243717314007981</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.232475010013253</v>
+        <v>-1.239568455188142</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.310807458689702</v>
+        <v>-1.317884280595429</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.53845890780191</v>
+        <v>-1.54557115790076</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.270872175619488</v>
+        <v>-1.278117753614389</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.215770551185372</v>
+        <v>-1.223036729553947</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.426896206370067</v>
+        <v>-1.43414519864119</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.570979104194294</v>
+        <v>-1.564394261110692</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9351727375541472</v>
+        <v>-0.9401100704937164</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9365944475761268</v>
+        <v>-0.9416956195331423</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.211745046550476</v>
+        <v>-1.216795568671763</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.266880813368807</v>
+        <v>-1.271902602052997</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.007098925763309</v>
+        <v>-1.012265825625903</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9628293837733111</v>
+        <v>-0.9679845123774271</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.538517691201477</v>
+        <v>-1.543489042198118</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.648092661184819</v>
+        <v>-1.653076767721004</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.589012917190693</v>
+        <v>-1.594026236256155</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.707356073380851</v>
+        <v>-1.712417757174492</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.519734723021884</v>
+        <v>-1.524883840311688</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.466732501557757</v>
+        <v>-1.471899276956343</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.732300960585242</v>
+        <v>-1.737422905661425</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.872191070027526</v>
+        <v>-1.867158923871052</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.00703730819226</v>
+        <v>-1.010792729870424</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.305265017641169</v>
+        <v>-1.309053420245874</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.588488234707526</v>
+        <v>-1.592219917717344</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.789697149455186</v>
+        <v>-1.793357225524346</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.424831496143028</v>
+        <v>-1.428651118240417</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.268826613471376</v>
+        <v>-1.272674717864476</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.685201084808583</v>
+        <v>-1.6889261321923</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.691842442570447</v>
+        <v>-1.695603981265698</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.513948644079946</v>
+        <v>-1.517773542254403</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.617575391067064</v>
+        <v>-1.621435981099943</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.646422600669943</v>
+        <v>-1.650292290688064</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.594701461828031</v>
+        <v>-1.598587154604402</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.680146765573909</v>
+        <v>-1.684040458030339</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.66701351618611</v>
+        <v>-1.663077291217988</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.151055213120991</v>
+        <v>-1.15401615116162</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.328910545123541</v>
+        <v>-1.331921128123064</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.707849248282741</v>
+        <v>-1.710772120302529</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.773009149675396</v>
+        <v>-1.77590583533533</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.480081340779741</v>
+        <v>-1.483102169068282</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.468612826815907</v>
+        <v>-1.471620064607229</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.658169150930817</v>
+        <v>-1.661126211237857</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.625643610368051</v>
+        <v>-1.628641773115788</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.5494989908684</v>
+        <v>-1.552525773315054</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.506195856236346</v>
+        <v>-1.509291319183923</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.633924232561327</v>
+        <v>-1.636995819088121</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.522469501952109</v>
+        <v>-1.525574414332397</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.683952829325477</v>
+        <v>-1.687037315940088</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.629573616697769</v>
+        <v>-1.626314175435809</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9598735053951586</v>
+        <v>-0.9622582347576625</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.225127707414465</v>
+        <v>-1.227518790264845</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.402023083314539</v>
+        <v>-1.404384362188239</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.66183717991165</v>
+        <v>-1.664117965228087</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.257990784807916</v>
+        <v>-1.260417211228635</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.379659233085462</v>
+        <v>-1.382036657634501</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.506934704690664</v>
+        <v>-1.509280912226494</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.552781946383995</v>
+        <v>-1.555139992727646</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.540229123182826</v>
+        <v>-1.54259527105426</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.417426169346932</v>
+        <v>-1.419872614432627</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.548280415660322</v>
+        <v>-1.550700732011158</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.643148311470071</v>
+        <v>-1.645540732798501</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.641044945984284</v>
+        <v>-1.643460809299938</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.607697930058926</v>
+        <v>-1.605005281926466</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6561311673347987</v>
+        <v>-0.6581454192051339</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8502420117376488</v>
+        <v>-0.8522704265434839</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.145965399804503</v>
+        <v>-1.14792850274155</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.534141824962312</v>
+        <v>-1.535991614835019</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.159101797214433</v>
+        <v>-1.161080534368132</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.296000042946794</v>
+        <v>-1.297928954218165</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.393851319437523</v>
+        <v>-1.395757393559045</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.39636313609919</v>
+        <v>-1.398289224518045</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.470361009134322</v>
+        <v>-1.47226996067355</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.405482492593734</v>
+        <v>-1.407446543034574</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.454211016213939</v>
+        <v>-1.456171099129115</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.545088356538763</v>
+        <v>-1.547022546238409</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.612205075341187</v>
+        <v>-1.614139200254186</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.431444309316497</v>
+        <v>-1.429203837530295</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5871202374213027</v>
+        <v>-0.5887298067390887</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5228817234221239</v>
+        <v>-0.5245639972365268</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8759024381359382</v>
+        <v>-0.8775027646866462</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.30339692662367</v>
+        <v>-1.304877247598647</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8458895074045216</v>
+        <v>-0.8475135515482037</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9427584070995962</v>
+        <v>-0.9443468762298295</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.067408150455506</v>
+        <v>-1.068966366389922</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.05611189511658</v>
+        <v>-1.057689863455131</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.129637323873808</v>
+        <v>-1.13119817194849</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.091393989528854</v>
+        <v>-1.092994935834071</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.144595633075753</v>
+        <v>-1.14618988363609</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.20441247391031</v>
+        <v>-1.20599011601076</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.172470471012367</v>
+        <v>-1.17407197813759</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.016902786377869</v>
+        <v>-1.015145987548983</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6021223905349657</v>
+        <v>-0.6034193594291608</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.228113451959203</v>
+        <v>-0.2295555066562471</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7418849041631432</v>
+        <v>-0.7432017790699845</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.023853047019365</v>
+        <v>-1.025091861566558</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6947153889021536</v>
+        <v>-0.6960576192735033</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6228767231701369</v>
+        <v>-0.6242305548921365</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7198869265519789</v>
+        <v>-0.7212179658165212</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8524091421001643</v>
+        <v>-0.853718558300784</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.9523011492759323</v>
+        <v>-0.9535863234883664</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9601643255889201</v>
+        <v>-0.9614718206392823</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.070068962768083</v>
+        <v>-1.071353547117511</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9675029752507811</v>
+        <v>-0.9688147132837344</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9721305107912173</v>
+        <v>-0.9734534767930541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7342530322334824</v>
+        <v>-0.7328388142130819</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4307751348313857</v>
+        <v>-0.4318426815393082</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1222488096432812</v>
+        <v>-0.1234337162874795</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4768921340236929</v>
+        <v>-0.4779939053237072</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6722143898390485</v>
+        <v>-0.673262784827557</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3079441744048594</v>
+        <v>-0.3091004472569452</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3099531897485903</v>
+        <v>-0.3111028322923772</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3020350624615702</v>
+        <v>-0.3031892801713738</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5980457420593623</v>
+        <v>-0.5991336862574528</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6447692080013354</v>
+        <v>-0.6458468892869007</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6431333999440056</v>
+        <v>-0.6442312852613128</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.7024860657349237</v>
+        <v>-0.7035736336395644</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5749958342260015</v>
+        <v>-0.5761165882557719</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6139856407433228</v>
+        <v>-0.6151062867480803</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3233813406627419</v>
+        <v>-0.322310497334378</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3874</v>
+        <v>3875</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3452520583113454</v>
+        <v>-0.3461423679829139</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.06486782612328312</v>
+        <v>-0.0658608063869579</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3428664827566621</v>
+        <v>-0.343795793479309</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3788963022199709</v>
+        <v>-0.3798143879308782</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1823211919753902</v>
+        <v>-0.1833004307338797</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1799009627784685</v>
+        <v>-0.1808757604891724</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2248432072803865</v>
+        <v>-0.2258085081819985</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4718022510890663</v>
+        <v>-0.4727131566738834</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5702626369750377</v>
+        <v>-0.5711497900691924</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6069135411494884</v>
+        <v>-0.6078076492354114</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6683945581597186</v>
+        <v>-0.6692771323550986</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.4648653719861287</v>
+        <v>-0.465800277944048</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.535241491636377</v>
+        <v>-0.5361666197579495</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.27103150880302</v>
+        <v>-0.2701433434453335</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.300789397523026</v>
+        <v>-0.30149383083846</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1242817100505036</v>
+        <v>-0.1250552287946292</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3532917480639952</v>
+        <v>-0.3540134677852649</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4629811347635169</v>
+        <v>-0.4636734725508092</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3026186283506931</v>
+        <v>-0.3033600386114443</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2958859723370963</v>
+        <v>-0.29662504021735</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3160564195377376</v>
+        <v>-0.3167920139890938</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6177358844238441</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.715014769737877</v>
+        <v>-0.7156577039718002</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7382831181253025</v>
+        <v>-0.738933201509731</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.7256704028358598</v>
+        <v>-0.7263271162123388</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4992301199456151</v>
+        <v>-0.4999442325009369</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4984969889584505</v>
+        <v>-0.4992179575434861</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2599237297338561</v>
+        <v>-0.2592052923803152</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3991</v>
+        <v>3992</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02091084768250084</v>
+        <v>-0.02149031268167079</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2042561157890432</v>
+        <v>0.2036021721061161</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02285799091382756</v>
+        <v>0.0222446530257443</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1581803689478818</v>
+        <v>-0.1587473152895953</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.01695127776451244</v>
+        <v>0.01633426409395611</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.04696587429226895</v>
+        <v>-0.04756388822546853</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.01800183245745046</v>
+        <v>-0.01860833101251558</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2463367602183482</v>
+        <v>-0.2468916656655722</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.318618881851009</v>
+        <v>-0.3191566715189396</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3790306989427847</v>
+        <v>-0.379563163450328</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.394576557493501</v>
+        <v>-0.3951077057704282</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2710664715884477</v>
+        <v>-0.2716284424244648</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1762977977970763</v>
+        <v>-0.1768885022473512</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1128736401757919</v>
+        <v>-0.1123568026217541</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1160101091741481</v>
+        <v>0.1155231386051128</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2492681262023169</v>
+        <v>0.2487338892635549</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.0658209192492194</v>
+        <v>0.06532837190408003</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1122017645890594</v>
+        <v>-0.1126493546188527</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.03129269890835928</v>
+        <v>0.03080465639687446</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.06992813375654094</v>
+        <v>0.06943289315606194</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.04828099932257857</v>
+        <v>0.04779014081941568</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.03368346449828863</v>
+        <v>-0.03415834830091313</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1058038363222025</v>
+        <v>-0.1062616186633889</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.09942983445117193</v>
+        <v>-0.0998968800665736</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1415314803315155</v>
+        <v>-0.1419901189008712</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.01882072605758367</v>
+        <v>-0.01930972134756104</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.04621992432540623</v>
+        <v>0.04571086807928282</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1115021731461141</v>
+        <v>0.1118574407993549</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07602319933760526</v>
+        <v>0.07562280919032105</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2235665223102785</v>
+        <v>0.2231179403310009</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.03886474768305703</v>
+        <v>0.03845851328966887</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.08813144417118934</v>
+        <v>-0.08850568333804887</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1005656021553563</v>
+        <v>0.1001408222969218</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1407472282817466</v>
+        <v>0.1403145267388481</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.09412022216750415</v>
+        <v>0.0936981798840435</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.03452043440175601</v>
+        <v>0.0341094603591543</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.01175583876761266</v>
+        <v>0.01134982904614645</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.03773594689531024</v>
+        <v>0.03731713147875126</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.05459159854164852</v>
+        <v>-0.05498935921721682</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.09227277445899773</v>
+        <v>0.09183886847533529</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1791294562177299</v>
+        <v>0.1786708568085018</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2455363837594149</v>
+        <v>0.2457947656195429</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.06344937247413895</v>
+        <v>0.06311528062025218</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2268529713778946</v>
+        <v>0.2264689554328925</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.04112303219979907</v>
+        <v>0.04078190035945539</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.06012701744735693</v>
+        <v>-0.06044273440990366</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1250152013501094</v>
+        <v>0.1246507207290719</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1664632791744367</v>
+        <v>0.1660902876256287</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1196558226381796</v>
+        <v>0.1192936114010621</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05806433472051253</v>
+        <v>0.05771420257116944</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.08414966261894108</v>
+        <v>0.08379259925767713</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1303726074216485</v>
+        <v>0.1299988624147161</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.06204411057015591</v>
+        <v>0.06168569893297615</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1838513224805212</v>
+        <v>0.1834630739278182</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2437017104218029</v>
+        <v>0.2432960356104843</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.286478510410447</v>
+        <v>0.2866743885950385</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_cross_7_21.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_7_21.xlsx
@@ -575,46 +575,46 @@
         <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.507947962359694</v>
+        <v>3.478877431324449</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.073797154750594</v>
+        <v>-6.075030615857621</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.48022574335161</v>
+        <v>-2.480396429851496</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.350932390789474</v>
+        <v>-2.351440845198994</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.888459768312998</v>
+        <v>-2.840041591741986</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.592260430777003</v>
+        <v>-2.568366147109785</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.315700231080719</v>
+        <v>1.363632007003382</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8498828466997495</v>
+        <v>0.8990567044686628</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.784265266747838</v>
+        <v>4.857443305993115</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.055770766593895</v>
+        <v>-3.956537042479013</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.732590109557108</v>
+        <v>3.832428386226205</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2302777459900724</v>
+        <v>-0.1066448164355975</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6504667324736459</v>
+        <v>-0.5018156432977392</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.575017946877246</v>
+        <v>7.747016706443908</v>
       </c>
     </row>
     <row r="7">
@@ -627,722 +627,722 @@
         <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.44833966890795</v>
+        <v>10.41933209747844</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.459524247576162</v>
+        <v>1.458350635352588</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.759324500520478</v>
+        <v>4.759207188493463</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.89040091708285</v>
+        <v>4.889941043146948</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.74555235067832</v>
+        <v>11.79405772917206</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12.04536690233682</v>
+        <v>12.06933940227265</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.569272110210193</v>
+        <v>4.617218339539818</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.802466549448816</v>
+        <v>7.851667718905176</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>22.53990545948547</v>
+        <v>22.6131427712666</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>29.0965094916707</v>
+        <v>29.19583138986653</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>21.49708882436887</v>
+        <v>21.59696238520601</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>17.8348191567237</v>
+        <v>17.95847573268843</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21.12190231585905</v>
+        <v>21.27056765439701</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>17.64909202095132</v>
+        <v>14.11738707681427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.09796</t>
+          <t>X ≈ -0.0979</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6644072672884889</v>
+        <v>0.6127305031639949</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.216423380798034</v>
+        <v>-4.080653943104174</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-7.836312307913232</v>
+        <v>-7.591297182479465</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.485433566061644</v>
+        <v>-4.346418354092265</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.616352404719983</v>
+        <v>4.518366679701423</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.701869201815356</v>
+        <v>1.673105106430214</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.829341697808097</v>
+        <v>-4.625988065617904</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.126260996562017</v>
+        <v>1.148589232686227</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.73279477061175</v>
+        <v>10.47512352402277</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>16.30291410933519</v>
+        <v>15.8985173383367</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>19.32202205460639</v>
+        <v>18.82103289861291</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.68732341906486</v>
+        <v>9.51349336428634</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.48206623816361</v>
+        <v>12.24496875288173</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.31695343074821</v>
+        <v>9.372016706443908</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.0883</t>
+          <t>X ≈ -0.08828</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.141199593045364</v>
+        <v>-1.155125524525168</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.425175704054446</v>
+        <v>5.350334905437371</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.762479000616239</v>
+        <v>7.65373209471084</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.263627327532618</v>
+        <v>9.133068156419355</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.619630920721249</v>
+        <v>4.602357326539803</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5503084219729146</v>
+        <v>-0.5184660946850599</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.37405028087322</v>
+        <v>-3.276817746580541</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.624387473364784</v>
+        <v>1.654537657714407</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.302172717475038</v>
+        <v>4.317075990775137</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.918240321121147</v>
+        <v>8.895093395826862</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.975204605582505</v>
+        <v>5.992616815849864</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.85986194830613</v>
+        <v>12.8056109353816</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.362980926787074</v>
+        <v>5.658726616273192</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.958579590712866</v>
+        <v>7.260530219957417</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.07867</t>
+          <t>X ≈ -0.07865</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>65</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.309171320073673</v>
+        <v>-6.335068073557494</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.289347497120346</v>
+        <v>1.287541662691361</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.034848214047095</v>
+        <v>7.031034482459617</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.0959868240936</v>
+        <v>4.093300876979718</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.024176815823907</v>
+        <v>2.071485826853014</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.286270785433999</v>
+        <v>-2.261179715519283</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.371232271423459</v>
+        <v>-2.321987744835177</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.845878759506284</v>
+        <v>4.892675017394588</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1742073479979638</v>
+        <v>0.2473082762237127</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.212929998944503</v>
+        <v>-2.112538950528958</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8801051340883532</v>
+        <v>-0.7798327098807292</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.6925100730417455</v>
+        <v>0.8157448350414214</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.810820758189877</v>
+        <v>1.959010005827487</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.578828206969611</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.06903</t>
+          <t>X ≈ -0.06901</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4439720425968332</v>
+        <v>-0.4674402523428185</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.039400602624823</v>
+        <v>-1.028630866651916</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.492683857820758</v>
+        <v>-3.457258998289809</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.507180653084582</v>
+        <v>-8.417122351374488</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.877259583988412</v>
+        <v>-2.799356409232836</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.550703617279417</v>
+        <v>-1.509040732757818</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.817355970918705</v>
+        <v>-7.680742992035093</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.35036574571234</v>
+        <v>-10.18564959332665</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-14.53529582673414</v>
+        <v>-14.30166958056553</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-16.42822970779474</v>
+        <v>-16.14776775684327</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-12.51509542960492</v>
+        <v>-12.277709924616</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-16.02438128302604</v>
+        <v>-16.30234044378708</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-11.28989296108124</v>
+        <v>-11.60098933832671</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.971373805699137</v>
+        <v>-8.293799620086709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.0594</t>
+          <t>X ≈ -0.05937</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8591772556433952</v>
+        <v>0.2366004450330976</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3548321122972382</v>
+        <v>0.8492427183323557</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.769965858055926</v>
+        <v>-6.117572311077808</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.210903387150744</v>
+        <v>1.682091904830308</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.91249338409748</v>
+        <v>3.386751664925114</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.700841367705664</v>
+        <v>8.046462540376226</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.858974247321456</v>
+        <v>10.18237056635373</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.143796069391044</v>
+        <v>7.525677647749475</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.714029192129495</v>
+        <v>4.198467228184022</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6077782331153401</v>
+        <v>1.181189781442413</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.038425784126161</v>
+        <v>0.9772757598847903</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.29798258037296</v>
+        <v>-2.259306519109181</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.594537928067879</v>
+        <v>-1.556469099398214</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.492397783460348</v>
+        <v>-2.406829447401748</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.04976</t>
+          <t>X ≈ -0.04974</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>135</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.450233280086408</v>
+        <v>-4.735193040861219</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-6.332469563574421</v>
+        <v>-6.326415310575022</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-7.470324926239485</v>
+        <v>-7.46203663724021</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.382218388303919</v>
+        <v>-4.377820392634874</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9948485191376051</v>
+        <v>0.7068141786610624</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9266252690296497</v>
+        <v>-1.237684080588302</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.494928442305962</v>
+        <v>-2.77649373489146</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.966369285912251</v>
+        <v>-3.242317255846636</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.770130424177715</v>
+        <v>-4.019797232256188</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.467651251538072</v>
+        <v>-4.103891205092118</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.376056113502315</v>
+        <v>-8.009849641138807</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.415752035221061</v>
+        <v>-2.031425040482759</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.835902888534804</v>
+        <v>-2.427171747220491</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.054611682752387</v>
+        <v>-6.6233536639268</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.04013</t>
+          <t>X ≈ -0.04011</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>161</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.403870832615716</v>
+        <v>-3.173758230848406</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6739008462936056</v>
+        <v>-0.4466925182143555</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.068335305184824</v>
+        <v>-0.2266593309757567</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.9389870277680856</v>
+        <v>-0.3739295276985786</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.097708043258159</v>
+        <v>-1.484758926038644</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5598382294002562</v>
+        <v>-0.2534612715021467</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.748173079843049</v>
+        <v>-3.69424828733176</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.974430081915337</v>
+        <v>-2.920308725472189</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.657530016745383</v>
+        <v>-3.578227169710502</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.265212788230386</v>
+        <v>-3.161376487174451</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.469913946490728</v>
+        <v>-3.366473699463114</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.677771818980112</v>
+        <v>-4.551092128482523</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.961276709560607</v>
+        <v>-6.810438682484218</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-7.977777084178655</v>
+        <v>-7.805778324611993</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03049</t>
+          <t>X ≈ -0.03048</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.363956827271259</v>
+        <v>-0.74801787876698</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.530080029960097</v>
+        <v>-2.342032339802238</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.175532571607285</v>
+        <v>-4.722017289162714</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.045960168343306</v>
+        <v>-4.591302292985041</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.986614530507993</v>
+        <v>-1.516432845520278</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.589525900999526</v>
+        <v>-2.13450700574495</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4744277529313976</v>
+        <v>0.9223169921600203</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8957712051539914</v>
+        <v>-0.6335692557567043</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.606721444197547</v>
+        <v>-1.562051862594878</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.907090690977853</v>
+        <v>-2.831278227086543</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.012692750138847</v>
+        <v>-3.928396245438122</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.527864147333069</v>
+        <v>-3.425665246508338</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.398465451096826</v>
+        <v>-4.268280571058746</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.470027098167797</v>
+        <v>-1.3422690078418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02085</t>
+          <t>X ≈ -0.02084</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>251</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-6.065007180237139</v>
+        <v>-6.307301966926367</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.898048331121601</v>
+        <v>-4.899163317797083</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.511146280018451</v>
+        <v>-2.907716365516272</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.778962154757302</v>
+        <v>-2.777046374721472</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9296470719138199</v>
+        <v>-0.8798959257269914</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5626208585218464</v>
+        <v>0.5861965630081087</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8746159321894069</v>
+        <v>0.9222615309813023</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.822768662506491</v>
+        <v>1.648235291315459</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.761786505983714</v>
+        <v>1.435648638436817</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9118677096537553</v>
+        <v>0.6134361946675142</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.496011172907608</v>
+        <v>3.19538484290576</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.05526804525509732</v>
+        <v>-0.3290467246244617</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7198002249374724</v>
+        <v>0.4703183861908045</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.44490237184786</v>
+        <v>-1.671309986783086</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01122</t>
+          <t>X ≈ -0.0112</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.144378569316331</v>
+        <v>3.223106001880971</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.488989819121471</v>
+        <v>5.26482846497683</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.486218718028262</v>
+        <v>4.264054478949852</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6582787429636596</v>
+        <v>0.7636591076726162</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.253758696662601</v>
+        <v>2.091651182435406</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.077057642472568</v>
+        <v>4.484019070522749</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.939676972020635</v>
+        <v>3.210467831174924</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.862852230672843</v>
+        <v>2.136590348534241</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.192113976589091</v>
+        <v>1.492749862442658</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.866585424161748</v>
+        <v>2.046890449359147</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.661884265901477</v>
+        <v>1.712870949893166</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.391384369476391</v>
+        <v>1.468631323286395</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.885867662504303</v>
+        <v>1.982520659555888</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.33111550785285</v>
+        <v>3.443986403413604</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001583</t>
+          <t>X ≈ -0.00157</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.837669577445553</v>
+        <v>-5.143121819841092</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-6.299220680019928</v>
+        <v>-6.442185407809106</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.699651437339611</v>
+        <v>-6.838421648844857</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-9.197170993226628</v>
+        <v>-9.614418962527644</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.15635374835633</v>
+        <v>-10.68209629646591</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-9.11651432554325</v>
+        <v>-9.825677891491864</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.160408358278943</v>
+        <v>-7.855901955052566</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-8.210567381074291</v>
+        <v>-8.616049411234414</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.105368779579571</v>
+        <v>-7.493042818497258</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.789106817891877</v>
+        <v>-7.160431388793029</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.119172407639013</v>
+        <v>-6.20271894491426</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.335523118257456</v>
+        <v>-4.526451677005802</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.17258359256212</v>
+        <v>-4.464642316303248</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.279209458370566</v>
+        <v>-6.543680967974765</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.008053</t>
+          <t>X ≈ 0.008064</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.648554221910757</v>
+        <v>2.464236957146007</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.586976532859133</v>
+        <v>1.431349923292679</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.902628760423404</v>
+        <v>1.590137927798047</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.189312638020589</v>
+        <v>1.718655560307447</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8559407033758148</v>
+        <v>-1.262301964182889</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.229875865941402</v>
+        <v>-2.649827241235094</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.593137757240811</v>
+        <v>-2.988733830441795</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.667448740860486</v>
+        <v>-2.071885200069644</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8927763012830425</v>
+        <v>-1.278702411270899</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3499374374458384</v>
+        <v>-0.7204706961962302</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2810160003943167</v>
+        <v>-0.09333777503798046</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.151048748849917</v>
+        <v>0.7959781120480116</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.28800095960343</v>
+        <v>0.9537188352238744</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6780820137296146</v>
+        <v>0.5337203075519454</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.01769</t>
+          <t>X ≈ 0.0177</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.208896439575824</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.50130446980841</v>
+        <v>2.656022384722945</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.754884733405028</v>
+        <v>3.915176958391768</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.357637349520921</v>
+        <v>6.524399842581659</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.797369774447112</v>
+        <v>3.004847671326679</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.99584270518119</v>
+        <v>2.17570481549005</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8122312470137985</v>
+        <v>1.013120351608819</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.542964801029257</v>
+        <v>2.751144340536896</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.481982644506537</v>
+        <v>2.714171731400029</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.632063848176678</v>
+        <v>1.890343150585046</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.152637415191215</v>
+        <v>1.410720609384988</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6375650180959909</v>
+        <v>0.9179231594221164</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.15621220884379</v>
+        <v>-0.8546452354612697</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4431498150091144</v>
+        <v>0.7718100948736577</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7326642822826059</v>
+        <v>-0.5937355182667758</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.267504937917401</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.58477560625532</v>
+        <v>-6.751835260726878</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.104900113016605</v>
+        <v>-6.273519163763069</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.146686169608849</v>
+        <v>-3.278447747223737</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.849312139973762</v>
+        <v>-3.005662228404773</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.332623897841323</v>
+        <v>-4.460046540626749</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.498993240928762</v>
+        <v>-5.622743412508349</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.161373998850138</v>
+        <v>-4.265987798648624</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.263041046928208</v>
+        <v>-3.34765610071797</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.817392554838754</v>
+        <v>-3.900228604003182</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.783014402483431</v>
+        <v>-3.842061866638289</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.552815605447194</v>
+        <v>-4.585651848951251</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.676730304871008</v>
+        <v>-4.685039042685013</v>
       </c>
     </row>
     <row r="22">
@@ -1404,153 +1404,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.004725554343935</v>
+        <v>-2.270877375126275</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.473054504550511</v>
+        <v>-6.246398957889674</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.867825889305607</v>
+        <v>-6.640136946204429</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-9.118553126669568</v>
+        <v>-8.902597402597351</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.275890298812939</v>
+        <v>-6.999502045941668</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.549944840606365</v>
+        <v>-5.291309828558148</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.729893295110628</v>
+        <v>-3.438090319697487</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.292200034135462</v>
+        <v>-1.990047481994701</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.44842028589634</v>
+        <v>-0.1131444930453753</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3459581298452932</v>
+        <v>0.0199647251827102</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.40780214524834</v>
+        <v>-3.05498911948257</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.373423992893073</v>
+        <v>-2.996822382117735</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9364319890635713</v>
+        <v>-0.5211669115523136</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.194065565924859</v>
+        <v>1.641753548549175</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.04659</t>
+          <t>X ≈ 0.0466</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>153</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.114902958638815</v>
+        <v>-4.144098752991447</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.804520424251848</v>
+        <v>-1.805707210696504</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.160076122732384</v>
+        <v>-4.160229512736706</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.415471894176697</v>
+        <v>-1.4159663865547</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.607356218514077</v>
+        <v>-2.558810298748305</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.577956045088214</v>
+        <v>-5.553998636138601</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.087503005661645</v>
+        <v>-1.039491326671325</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2473821069646434</v>
+        <v>-0.1981345445709266</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.26914857721291</v>
+        <v>-2.195891467433214</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8025012539082823</v>
+        <v>0.9018485792028557</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.362984218077472</v>
+        <v>-1.263076182058796</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.0214165232384147</v>
+        <v>0.1022800977898299</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.748756919035486</v>
+        <v>-1.600067371257659</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.05623</t>
+          <t>X ≈ 0.05624</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>141</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.547452763791846</v>
+        <v>3.518256969439214</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.227046812572034</v>
+        <v>1.225860026127378</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.796814434909315</v>
+        <v>5.796661044904994</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9625005714053572</v>
+        <v>0.9620060790273541</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.970310309089719</v>
+        <v>4.018856228855491</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7215850479447496</v>
+        <v>0.7455424568943627</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.055314404990717</v>
+        <v>2.103326083981038</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1698060448918426</v>
+        <v>0.2190536072855593</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.309615827942991</v>
+        <v>-1.236358718163295</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6773448083511795</v>
+        <v>0.7766921336457528</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4726436500910722</v>
+        <v>0.5725516861097475</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-4.457517204645811</v>
+        <v>-4.333820583617566</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6223489090230885</v>
+        <v>-0.4736593612452609</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.105833116952503</v>
+        <v>-0.933834357385841</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>109</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.986973877722527</v>
+        <v>8.957778083369895</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>11.0455125553009</v>
+        <v>11.04432576885625</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.981016399903602</v>
+        <v>6.980863009899281</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.524085580189272</v>
+        <v>2.523591087811269</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.985796027093578</v>
+        <v>2.03434194685935</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.365738864068106</v>
+        <v>1.389696273017719</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.198459697462496</v>
+        <v>2.246471376452817</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.56625343899686</v>
+        <v>3.615501001390577</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.7529777044924231</v>
+        <v>0.8262348142721194</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.014372284497981</v>
+        <v>-0.9150249592034072</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.533220135223431</v>
+        <v>1.633128171242106</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.567598287578797</v>
+        <v>1.691294908607041</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6874149510557146</v>
+        <v>-0.538725403277887</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.125476662473524</v>
+        <v>4.297475422040186</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.0755</t>
+          <t>X ≈ 0.07551</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>107</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.724691446101154</v>
+        <v>1.695495651748523</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>10.39387918481303</v>
+        <v>10.39269239836837</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.129948921553272</v>
+        <v>8.12979553154895</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.391015186637063</v>
+        <v>6.39052069425906</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>9.591043390550716</v>
+        <v>9.639589310316488</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10.82299685943813</v>
+        <v>10.84695426838775</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.803707060919635</v>
+        <v>9.851718739909956</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>10.27121785638517</v>
+        <v>10.32046541877889</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.21023569986245</v>
+        <v>10.28349280964215</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.360316903532535</v>
+        <v>9.459664228827108</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.155615745272456</v>
+        <v>9.255523781291132</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.12457333688001</v>
+        <v>10.24826995790826</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>13.4427402405759</v>
+        <v>13.59142978835373</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>12.7338964515502</v>
+        <v>12.90589521111686</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>82</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.261403835412366</v>
+        <v>-1.290599629764998</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.98106860810914</v>
+        <v>12.97988182166448</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.269224052622455</v>
+        <v>5.269070662618134</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>11.49701017182043</v>
+        <v>11.49651567944242</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.080671838236974</v>
+        <v>6.129217758002746</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>13.69511903860374</v>
+        <v>13.71907644755335</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14.82992087445945</v>
+        <v>14.87793255344977</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.26529125506309</v>
+        <v>8.314538817456807</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.984796903418363</v>
+        <v>7.05805401319806</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.915365911966553</v>
+        <v>5.014713237261127</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.271640363462453</v>
+        <v>2.371548399481128</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.623091686549493</v>
+        <v>9.746788307577738</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.983428638114134</v>
+        <v>8.132118185891962</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.86770087370638</v>
+        <v>12.03969963327304</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>76</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>8.045399758939254</v>
+        <v>8.016203964586623</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.118424192191256</v>
+        <v>5.1172374057466</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.61838964954152</v>
+        <v>12.6182362595372</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>16.69598321418251</v>
+        <v>16.69548872180451</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>18.7892726084552</v>
+        <v>18.83781852822097</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.13927821703768</v>
+        <v>15.1632356259873</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20.31772575250844</v>
+        <v>20.36573743149876</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.95592026661637</v>
+        <v>12.00516782901008</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.52651705746193</v>
+        <v>14.59977416724163</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>14.99238773481636</v>
+        <v>15.09173506011093</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>17.41926552392455</v>
+        <v>17.51917355994323</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>18.76943314996412</v>
+        <v>18.89312977099237</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>17.03349282296649</v>
+        <v>17.18218237074432</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.89080742056152</v>
+        <v>20.06280618012818</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>57</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.413820811570915</v>
+        <v>5.384625017218283</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.802634718507086</v>
+        <v>3.80144793206243</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.671021228488883</v>
+        <v>8.670867838484561</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>19.32756216155092</v>
+        <v>19.32706766917292</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.26295681898155</v>
+        <v>8.311502738747322</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.560330848616637</v>
+        <v>8.58428825756625</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.966848559525907</v>
+        <v>5.014860238516228</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.00855184556373</v>
+        <v>8.057799407957447</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.438797759216392</v>
+        <v>4.512054868996088</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.834492997974259</v>
+        <v>1.933840323268832</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.629791839714009</v>
+        <v>1.729699875732685</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.752791068580486</v>
+        <v>4.901480616358313</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.224140753894787</v>
+        <v>3.396139513461449</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>58</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.691497762569142</v>
+        <v>2.662301968216511</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.092102123598139</v>
+        <v>-4.093288910042794</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.038597646284302</v>
+        <v>-1.038751036288623</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.080786295799342</v>
+        <v>-6.081280788177345</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-8.34321377992957</v>
+        <v>-8.294667860163798</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-8.045839750294483</v>
+        <v>-8.02188234134487</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-6.406412178526068</v>
+        <v>-6.358400499535747</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-10.32175668438182</v>
+        <v>-10.2725091219881</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-10.38273884090454</v>
+        <v>-10.30948173112485</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-9.508519706199927</v>
+        <v>-9.409172380905353</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.540807071356667</v>
+        <v>-4.440899035337992</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.782290987966917</v>
+        <v>-2.658594366938672</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.969971951823176</v>
+        <v>2.118661499601004</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4715696710152244</v>
+        <v>0.6435684305818867</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>59</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>18.70552464743175</v>
+        <v>18.67632885307912</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>22.17908431707978</v>
+        <v>22.17789753063513</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25.17414344079936</v>
+        <v>25.17399005079504</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>20.21962282167582</v>
+        <v>20.21912832929782</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21.37624852281747</v>
+        <v>21.42479444258324</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16.58887678974068</v>
+        <v>16.61283419869029</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>19.893996938949</v>
+        <v>19.94200861793932</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>24.51167405787417</v>
+        <v>24.56092162026788</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>26.14560715558865</v>
+        <v>26.21886426536835</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>23.60077310502149</v>
+        <v>23.70012043031606</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>21.70115669252399</v>
+        <v>21.80106472854267</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.95587382793024</v>
+        <v>15.07957044895848</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>21.31538399156597</v>
+        <v>21.46407353934379</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.676712862131446</v>
+        <v>9.848711621698108</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.882256850760797</v>
+        <v>4.881070064316141</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.487485466005758</v>
+        <v>4.487332076001437</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.61771060959412</v>
+        <v>4.617216117216117</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.515318492395856</v>
+        <v>1.563864412161628</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>21.77373403179856</v>
+        <v>21.82298159419228</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>21.71275187527573</v>
+        <v>21.78600898505542</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>28.5551407712536</v>
+        <v>28.65448809654818</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>25.78633704889084</v>
+        <v>25.88624508490952</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>25.82071520124614</v>
+        <v>25.94441182227438</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.8364617838302</v>
+        <v>22.98515133160803</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>23.06219743405673</v>
+        <v>23.2341961936234</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>24</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-6.647582697201024</v>
+        <v>-6.676778491553655</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.817725752508366</v>
+        <v>7.865737431498687</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>19.78967495219888</v>
+        <v>19.86293206197858</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>23.10642282253569</v>
+        <v>23.20577014783026</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.56838833094214</v>
+        <v>14.66829636696082</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.76943314996412</v>
+        <v>18.89312977099237</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>22.51594896331737</v>
+        <v>22.6646385110952</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>22.74168461354395</v>
+        <v>22.91368337311061</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.907897876401826</v>
+        <v>0.9067110899571702</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5131264916467373</v>
+        <v>0.5129731016424159</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.317725752508331</v>
+        <v>5.365737431498651</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.78967495219881</v>
+        <v>14.8629320619785</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.93975615586896</v>
+        <v>19.03910348116354</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>23.7350549976088</v>
+        <v>23.83496303362747</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>18.76943314996412</v>
+        <v>18.89312977099237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.34928229665071</v>
+        <v>13.49797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.575017946877217</v>
+        <v>8.74701670644388</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.03865344108990598</v>
+        <v>0.03929046835526862</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1041298313810231</v>
+        <v>0.1038804408600384</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.03263953870074232</v>
+        <v>-0.0325480113670622</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.0359629302483313</v>
+        <v>-0.0358537946428612</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.02670752778097807</v>
+        <v>0.02540287370009509</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09261490187984833</v>
+        <v>0.0917574679640154</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1437914065994903</v>
+        <v>0.1421850249509262</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3272559815469194</v>
+        <v>0.3251246124643146</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4024200502380708</v>
+        <v>0.3994756943422715</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.4732202402033892</v>
+        <v>0.4694213295743239</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4049912408653</v>
+        <v>0.4013606858651855</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.355157947609456</v>
+        <v>0.351055407000203</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.365965319221857</v>
+        <v>0.3611967037385426</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3357541431962616</v>
+        <v>0.3304724088423399</v>
       </c>
     </row>
     <row r="7">
@@ -2266,829 +2266,829 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4050</v>
+        <v>4061</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.01723804281046171</v>
+        <v>0.01811596107276614</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1422651831472663</v>
+        <v>0.1419185537430678</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.0175309818819116</v>
+        <v>-0.0174787647622594</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.02167299530673006</v>
+        <v>-0.02159876478226153</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04470238763341428</v>
+        <v>0.0430428913401073</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.109188206402429</v>
+        <v>0.1081335059785076</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.136557401510089</v>
+        <v>0.1346656517543394</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3240298897867149</v>
+        <v>0.3215914181032957</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3753716229756705</v>
+        <v>0.3720319144133768</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.5011769748132409</v>
+        <v>0.4966680568093196</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3844505071079354</v>
+        <v>0.3802386241786522</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3587717481872303</v>
+        <v>0.3538730641255228</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.372239591145906</v>
+        <v>0.366509510602846</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2910673295932966</v>
+        <v>0.2848152782242579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1028</t>
+          <t>X &gt; -0.1027</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4023</v>
+        <v>4034</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05276935065327848</v>
+        <v>-0.05150050786202343</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1334245182853309</v>
+        <v>0.1331075308864769</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04959041464970682</v>
+        <v>-0.04944964248608841</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.05463993431605729</v>
+        <v>-0.05447223399745837</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.03382680674943828</v>
+        <v>-0.03560792686054981</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.02907962455051916</v>
+        <v>0.02807585620163167</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.106807638364451</v>
+        <v>0.1046634399124429</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2738390397218708</v>
+        <v>0.2711917998282232</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2266163623279454</v>
+        <v>0.2231697445732479</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3092619914786283</v>
+        <v>0.3045814405493985</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2427549479317008</v>
+        <v>0.2382327883958695</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2414828394051156</v>
+        <v>0.2360435470082223</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2329801097719866</v>
+        <v>0.2265963797445281</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1745705195841794</v>
+        <v>0.1922323732758358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.09312</t>
+          <t>X &gt; -0.0931</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3992</v>
+        <v>4002</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.05833860795693369</v>
+        <v>-0.05681170035398253</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1672033972611757</v>
+        <v>0.1668007760558154</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.01087761608455651</v>
+        <v>0.01085498551985609</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.02023246873886819</v>
+        <v>-0.02015382424156797</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.0699379178605497</v>
+        <v>-0.07202151691802072</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.01608952512786743</v>
+        <v>0.01492219902838343</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1451394593617863</v>
+        <v>0.1424897388072353</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.267219530537993</v>
+        <v>0.2641761282011643</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.145030307554201</v>
+        <v>0.1411951016591146</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1850627891606038</v>
+        <v>0.1798922979384017</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09459430657224743</v>
+        <v>0.0896446815675489</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1681308709758937</v>
+        <v>0.1618610397236324</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1378594509593327</v>
+        <v>0.1304974502241976</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.08804399898145476</v>
+        <v>0.1188307993974291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.08349</t>
+          <t>X &gt; -0.08346</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3919</v>
+        <v>3928</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0381679389313021</v>
+        <v>-0.03612045213895243</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06926209121475324</v>
+        <v>0.06914763818051028</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1335130195548473</v>
+        <v>-0.1331299702031856</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1931647895165725</v>
+        <v>-0.1925923238772427</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1572914583597864</v>
+        <v>-0.1600826254760364</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.02663993343058024</v>
+        <v>0.02497075649650782</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2106921133646296</v>
+        <v>0.2069064276867465</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2419392907251918</v>
+        <v>0.2379829629302961</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.06759438106167437</v>
+        <v>0.06252524784175506</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02238813750632573</v>
+        <v>0.01570571921035935</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-0.02156202360986725</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.0682805525109984</v>
+        <v>-0.0763358778625971</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.02190286312175971</v>
+        <v>0.02635056674974834</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05856204801941089</v>
+        <v>-0.01571241779234356</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.07385</t>
+          <t>X &gt; -0.07383</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3854</v>
+        <v>3863</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06759625924572532</v>
+        <v>0.06986753527813505</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.04868462588422773</v>
+        <v>0.04864657382813675</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2544116911127361</v>
+        <v>-0.2536763562821633</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2655038800419192</v>
+        <v>-0.2647080520821845</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1940832170058471</v>
+        <v>-0.1976316675162622</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06564854700769729</v>
+        <v>0.06343821201838296</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2542378022621961</v>
+        <v>0.24945836173125</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1642911159792746</v>
+        <v>0.1596617142789469</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.06579629002617082</v>
+        <v>0.05941603302301246</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06008810607646353</v>
+        <v>0.05151620420468106</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.0003535627024859878</v>
+        <v>-0.008803132952969861</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.08111173846349118</v>
+        <v>-0.0913462962780045</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.008268300131852868</v>
+        <v>-0.006168942320940118</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.01605626173717667</v>
+        <v>0.02452123660181371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06421</t>
+          <t>X &gt; -0.06419</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3757</v>
+        <v>3765</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.08080417121770722</v>
+        <v>0.08385323599178207</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.07677732409167248</v>
+        <v>0.0766872615219043</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1708044512483085</v>
+        <v>-0.1702896102219427</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.05271637751724967</v>
+        <v>-0.05250709555345878</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1248077026067662</v>
+        <v>-0.1299108110253613</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1073802904029222</v>
+        <v>0.1043686068625007</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4626340215857425</v>
+        <v>0.4558752893990103</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4357634917003494</v>
+        <v>0.4289420617279092</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4427741807170733</v>
+        <v>0.4332238391668781</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4857912809355227</v>
+        <v>0.4731708730447011</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3227579520937667</v>
+        <v>0.3105468977463701</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.330519122814799</v>
+        <v>0.3306131795402862</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2830060123813496</v>
+        <v>0.295635147668051</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1893378829964831</v>
+        <v>0.2410406108263814</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.05458</t>
+          <t>X &gt; -0.05456</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3668</v>
+        <v>3674</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.06191780139385372</v>
+        <v>0.08006989466821324</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.07003062939420346</v>
+        <v>0.05755211003312866</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.01068303216273847</v>
+        <v>-0.0229834790902359</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.08337672622376147</v>
+        <v>-0.09547076159454093</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1985044846996473</v>
+        <v>-0.2170137738210869</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.07686672046947507</v>
+        <v>-0.09234629459361798</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2346421240692536</v>
+        <v>0.2149631853699177</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.273000432972303</v>
+        <v>0.2531655406805555</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3634007630464922</v>
+        <v>0.3399638640986851</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4828314012343213</v>
+        <v>0.4556342043827044</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3053930564964773</v>
+        <v>0.2940329275627533</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3942968358965118</v>
+        <v>0.394761979915117</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3285625583737186</v>
+        <v>0.3415092593945275</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2544072598543465</v>
+        <v>0.3066247630579468</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04494</t>
+          <t>X &gt; -0.04493</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3533</v>
+        <v>3539</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2725434441902976</v>
+        <v>0.263754691587252</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3146775374187669</v>
+        <v>0.3010772871402594</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2743584780836201</v>
+        <v>0.2607893879202834</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.08088696593045341</v>
+        <v>0.06788532775003375</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2441038777135276</v>
+        <v>-0.252254455817436</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04439646741099068</v>
+        <v>-0.04865581674413733</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3389421598633859</v>
+        <v>0.3290764049899479</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3967804816701275</v>
+        <v>0.3865055173776923</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5213477515195351</v>
+        <v>0.50627291976636</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6337838943348828</v>
+        <v>0.6295635432578379</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5989100782767878</v>
+        <v>0.6107958964168603</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4634608884300135</v>
+        <v>0.4873122053329482</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4112692765544779</v>
+        <v>0.447124386801427</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4954821416125981</v>
+        <v>0.5709782775091838</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03531</t>
+          <t>X &gt; -0.03529</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3372</v>
+        <v>3378</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4480780523058883</v>
+        <v>0.4275911571029809</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3618783439957838</v>
+        <v>0.3367169966317007</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3384669297758478</v>
+        <v>0.2840218461033146</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1295820172310016</v>
+        <v>0.08894281493986256</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1556014249695536</v>
+        <v>-0.1935116435896092</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.01978611044768286</v>
+        <v>-0.03889451472636551</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5340861555907637</v>
+        <v>0.5208334433155244</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5577427891248306</v>
+        <v>0.5441127089404034</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7208730542154598</v>
+        <v>0.7009456593773109</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8199459542082579</v>
+        <v>0.8102448176508474</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7931807390085694</v>
+        <v>0.8003578872210824</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7089349293235614</v>
+        <v>0.7274492976195859</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7632799241714778</v>
+        <v>0.7930295538100083</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9000476028677582</v>
+        <v>0.9702257058518455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02567</t>
+          <t>X &gt; -0.02566</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3150</v>
+        <v>3154</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5757833676284605</v>
+        <v>0.5110839992193092</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5656925532079029</v>
+        <v>0.5269642545141267</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7270726089209489</v>
+        <v>0.6395553801234755</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4943345141191031</v>
+        <v>0.4213381555153717</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.02655859657922832</v>
+        <v>-0.09955655505680028</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1613193605054946</v>
+        <v>0.1099378245216158</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5382906525400983</v>
+        <v>0.4923197099797036</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6601809182454375</v>
+        <v>0.6277527723811644</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.884913047436946</v>
+        <v>0.8616658384901044</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.068869155641082</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.131880394434198</v>
+        <v>1.136198383643304</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.007528388059363</v>
+        <v>1.022407337532293</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.127060074428485</v>
+        <v>1.152488484682102</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.06708143894074</v>
+        <v>1.134461221345617</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.01604</t>
+          <t>X &gt; -0.01602</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2899</v>
+        <v>2903</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.150753504749638</v>
+        <v>1.100617198496792</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.038751870892177</v>
+        <v>0.9961196181552339</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.007442716242018</v>
+        <v>0.9462605844485097</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7777417110449321</v>
+        <v>0.6978777755944137</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.05163223036419851</v>
+        <v>-0.03208663358308428</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1265740428090112</v>
+        <v>0.06875940793185009</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.5091710784828436</v>
+        <v>0.4551459596967575</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.55952223462711</v>
+        <v>0.5395195266861847</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8089919580629399</v>
+        <v>0.8120379766965726</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.097396721581312</v>
+        <v>1.108246928015987</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9271902166498478</v>
+        <v>0.9581564266075162</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.099546982320113</v>
+        <v>1.139257137601653</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.162321275608974</v>
+        <v>1.211470467018074</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.284572965849307</v>
+        <v>1.377054598279933</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0064</t>
+          <t>X &gt; -0.006388</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8964131620122302</v>
+        <v>0.8283974918832016</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.471004672518319</v>
+        <v>0.4486365557956802</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5636315421518319</v>
+        <v>0.5207370767977366</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7929824164244152</v>
+        <v>0.6894409937888142</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2293080578294493</v>
+        <v>-0.3044665322562636</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3774160858139552</v>
+        <v>-0.4975195227541107</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1990948695834263</v>
+        <v>0.1017622762191834</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3932475404602513</v>
+        <v>0.3346872798109999</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7601144698962443</v>
+        <v>0.7247333042145669</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.9992660741887107</v>
+        <v>0.987861245138717</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8334602873793173</v>
+        <v>0.861360549155421</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.062315296988629</v>
+        <v>1.097013266137999</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.070013529633997</v>
+        <v>1.112579459036155</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.023481579704942</v>
+        <v>1.111960351993844</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.003235</t>
+          <t>X &gt; 0.003247</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.7791736555643</v>
+        <v>1.749977861211669</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.513279042321109</v>
+        <v>1.512092255876453</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.681812000843728</v>
+        <v>1.65647085949</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.33096384349367</v>
+        <v>2.279628443305569</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.298957952875533</v>
+        <v>1.29710575975276</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9679657347547845</v>
+        <v>0.9420885879887209</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.332088409599933</v>
+        <v>1.329862992036801</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.717802530624681</v>
+        <v>1.716048168873186</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.971003497979822</v>
+        <v>1.992976905027881</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.198283983517101</v>
+        <v>2.2453815080694</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.903816218434649</v>
+        <v>1.951554961878593</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.893311067378846</v>
+        <v>1.964878649916137</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.877109944765621</v>
+        <v>1.973308167298491</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.14772889840328</v>
+        <v>2.293450084640412</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.01287</t>
+          <t>X &gt; 0.01288</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.612181882788278</v>
+        <v>1.611943849631217</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.499123130548419</v>
+        <v>1.527696100663796</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.639397224659085</v>
+        <v>1.669290018130681</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.358172394999727</v>
+        <v>2.388039155705101</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.712873746130882</v>
+        <v>1.79172363359686</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.582211392673415</v>
+        <v>1.636243627790535</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.086051060159512</v>
+        <v>2.164452634924807</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.368046086784759</v>
+        <v>2.448084542635691</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.52108212180827</v>
+        <v>2.625244695811524</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.687749735323244</v>
+        <v>2.818546735981549</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.215525837630203</v>
+        <v>2.346740335554664</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.035885798439246</v>
+        <v>2.190774310606926</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.990266780331829</v>
+        <v>2.17034871809021</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.430020622104642</v>
+        <v>2.633526342418214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.02251</t>
+          <t>X &gt; 0.02252</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1505</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.738353072455681</v>
+        <v>1.709157278103049</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.256735085704143</v>
+        <v>1.255548299259488</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.127744431846118</v>
+        <v>1.127591041841796</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.390859940882983</v>
+        <v>1.39036544850498</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.450577032305553</v>
+        <v>1.499122952071325</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.48217033104364</v>
+        <v>1.506127739993254</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.394137712641253</v>
+        <v>2.442149391631574</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.325740165200031</v>
+        <v>2.374987727593748</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.530538739574268</v>
+        <v>2.603795849353965</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.943078415005203</v>
+        <v>3.042425740299777</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.472596525847997</v>
+        <v>2.572504561866673</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.374084312754825</v>
+        <v>2.497780933783069</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.751275652132442</v>
+        <v>2.89996519991027</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.910566119634723</v>
+        <v>3.082564879201385</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.03214</t>
+          <t>X &gt; 0.03215</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.318099556012001</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.511671461307479</v>
+        <v>2.556957395375882</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.937244621261222</v>
+        <v>2.984237469458549</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.149504219320455</v>
+        <v>3.19622331691297</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.529180211753889</v>
+        <v>2.624872369721309</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.498416423505468</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.972360699185977</v>
+        <v>4.068528892910841</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.161567691166262</v>
+        <v>4.259510582445394</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.100585534643486</v>
+        <v>4.222537973308597</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.399149100905909</v>
+        <v>4.548134679849937</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.948344579233087</v>
+        <v>4.097688813594637</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.818653822646645</v>
+        <v>3.991651938480054</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.464950877454655</v>
+        <v>4.663817493032809</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.690686527681187</v>
+        <v>4.912862355048176</v>
       </c>
     </row>
     <row r="23">
@@ -3101,98 +3101,98 @@
         <v>1009</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.2177955651049</v>
+        <v>3.188599770752269</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.381634249047998</v>
+        <v>4.380447462603343</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.977943141795443</v>
+        <v>4.977789751791121</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.702816451885283</v>
+        <v>5.70232195950728</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.56987873228811</v>
+        <v>4.618424652053882</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.173496567671464</v>
+        <v>4.197453976621077</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.57540662465901</v>
+        <v>5.623418303649331</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.504770091873262</v>
+        <v>5.554017654266978</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.047355824349495</v>
+        <v>5.120612934129191</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.386733361022607</v>
+        <v>5.48608068631718</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.479356286013157</v>
+        <v>5.579264322031833</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.315518382867992</v>
+        <v>5.439215003896237</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.58912372380631</v>
+        <v>5.737813271584137</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.418427263031852</v>
+        <v>5.590426022598514</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.05141</t>
+          <t>X &gt; 0.05142</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>856</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.528429763858163</v>
+        <v>4.499233969505532</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.487337128738268</v>
+        <v>5.486150342293612</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.611257332768282</v>
+        <v>6.611103942763961</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.97512733616972</v>
+        <v>6.974632843791717</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.852725633541311</v>
+        <v>5.901271553307083</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.916454803363322</v>
+        <v>5.940412212312935</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.766323883349493</v>
+        <v>6.814335562339814</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.53290009937583</v>
+        <v>6.582147661769547</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.355095512946512</v>
+        <v>6.428352622726209</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.206111296055902</v>
+        <v>6.305458621350475</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.702344717234965</v>
+        <v>6.80225275325364</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.900684165809587</v>
+        <v>7.049373713587414</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.542307666503412</v>
+        <v>6.714306426070074</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>715</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.721881172262854</v>
+        <v>4.692685377910223</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.327478295982239</v>
+        <v>6.326291509537583</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.771867750388033</v>
+        <v>6.771714360383712</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8.160834152717655</v>
+        <v>8.160339660339652</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.223943201020568</v>
+        <v>6.272489120786339</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.940897650236074</v>
+        <v>6.964855059185687</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.695348130130746</v>
+        <v>7.743359809121067</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.787720045784567</v>
+        <v>7.836967608178284</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.866598029121924</v>
+        <v>7.939855138901621</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.296399512512352</v>
+        <v>7.395746837806925</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.930859193412999</v>
+        <v>8.030767229431675</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.384817765348735</v>
+        <v>8.50851438637698</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.38424733161574</v>
+        <v>8.532936879393567</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.050542422401712</v>
+        <v>8.222541181968374</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.07068</t>
+          <t>X &gt; 0.07069</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>606</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.95472753382208</v>
+        <v>3.925531739469449</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.478854972111392</v>
+        <v>5.477668185666737</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.734248603858006</v>
+        <v>6.734095213853685</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.174704770548672</v>
+        <v>9.174210278170669</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.986250200951325</v>
+        <v>7.034796120717097</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.94369023718707</v>
+        <v>7.967647646136683</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.684062386171732</v>
+        <v>8.732074065162053</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.547026745685329</v>
+        <v>8.596274308079046</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>9.146110595763204</v>
+        <v>9.219367705542901</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.791241304383846</v>
+        <v>8.890588629678419</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.081589651074154</v>
+        <v>9.181497687092829</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.611017308379964</v>
+        <v>9.734713929408208</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.756536098692429</v>
+        <v>8.928534858259091</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>499</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.432911624776267</v>
+        <v>4.403715830423636</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.424931944538095</v>
+        <v>4.423745158093439</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.434970179021533</v>
+        <v>6.434816789017212</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9.771608148261187</v>
+        <v>9.771113655883184</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.427707372720604</v>
+        <v>6.476253292486376</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.326283807165311</v>
+        <v>7.350241216114924</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.443978257518381</v>
+        <v>8.491989936508702</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.177310415334851</v>
+        <v>8.226557977728568</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.917931465224896</v>
+        <v>8.991188575004593</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.669215073704663</v>
+        <v>8.768562398999237</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.065716320254083</v>
+        <v>9.165624356272758</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.500896075815824</v>
+        <v>9.624592696844068</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.281146024105624</v>
+        <v>9.429835571883451</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.9036752615065</v>
+        <v>8.075674021073162</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>417</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.552657110952453</v>
+        <v>5.523461316599821</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.742430250502537</v>
+        <v>2.741243464057881</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.664205628337427</v>
+        <v>6.664052238333106</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.432320460175191</v>
+        <v>9.431825967797188</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.495949372307308</v>
+        <v>6.54449529207308</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.073898941510748</v>
+        <v>6.097856350460361</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.188229349630674</v>
+        <v>7.236241028620995</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.160009626707236</v>
+        <v>8.209257189100953</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.298068237570547</v>
+        <v>9.371325347350243</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.407382055149569</v>
+        <v>9.506729380444142</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.476867202721913</v>
+        <v>9.600563823750157</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.536332656362944</v>
+        <v>9.685022204140772</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.124178618340082</v>
+        <v>7.296177377906744</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>341</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.997089834568293</v>
+        <v>4.967894040215661</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.212883213645227</v>
+        <v>2.211696427200572</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.337173412467898</v>
+        <v>5.337020022463577</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.813439611774733</v>
+        <v>7.81294511939673</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.756088475101329</v>
+        <v>3.804634394867101</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.053462504736416</v>
+        <v>4.077419913686029</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.262007277435053</v>
+        <v>4.310018956425374</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.314000217226024</v>
+        <v>7.363247779619741</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.132783456597679</v>
+        <v>8.206040566377375</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.162630056162243</v>
+        <v>8.261977381456816</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.837694293796474</v>
+        <v>8.937602329815149</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.405796786327755</v>
+        <v>7.529493407356</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.865411328908777</v>
+        <v>8.014100876686605</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.278830263592788</v>
+        <v>4.45082902315945</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>284</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.913450166648751</v>
+        <v>4.88425437229612</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.89381336935957</v>
+        <v>1.892626582914914</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.668056069111564</v>
+        <v>4.667902679107243</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.502506564812606</v>
+        <v>5.502012072434603</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.851540955378887</v>
+        <v>2.900086875144659</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.148914985013974</v>
+        <v>3.172872393963587</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.120542653916814</v>
+        <v>4.168554332907135</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.174600770693452</v>
+        <v>7.223848333087169</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.874181994452371</v>
+        <v>8.947439104232068</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.432713902347871</v>
+        <v>9.532061227642444</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.28435077225669</v>
+        <v>10.38425880827536</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.501827516161306</v>
+        <v>7.625524137189551</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.490127367073256</v>
+        <v>8.638816914851084</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.490510904623719</v>
+        <v>4.662509664190381</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>226</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.483685739377151</v>
+        <v>5.45448994502452</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.430021770207127</v>
+        <v>3.428834983762471</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.132595518195458</v>
+        <v>6.132442128191137</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.475210042314785</v>
+        <v>8.474715549936782</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.724531108688126</v>
+        <v>5.773077028453898</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.021905138323213</v>
+        <v>6.045862547272826</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.822150531269422</v>
+        <v>6.870162210259743</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.66481640075703</v>
+        <v>11.71406396315074</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.81622362476521</v>
+        <v>13.88948073454491</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.29373845675394</v>
+        <v>14.39308578204852</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>14.08903729849375</v>
+        <v>14.18894533451243</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.14111456589333</v>
+        <v>10.26481118692157</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.16344158868611</v>
+        <v>10.31213113646394</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.521920601744498</v>
+        <v>5.69391936131116</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>167</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.8124971431183425</v>
+        <v>0.7833013487657112</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.193898530783805</v>
+        <v>-3.195085317228461</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5946579394909435</v>
+        <v>-0.5948113294952648</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.325986365774064</v>
+        <v>4.325491873396061</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1948824414208872</v>
+        <v>0.243428361186659</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.288663656684719</v>
+        <v>2.312621065634332</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.203953297418551</v>
+        <v>2.251964976408871</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.126106210518039</v>
+        <v>7.175353772911755</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.460333634833574</v>
+        <v>9.533590744613271</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.00562441934204</v>
+        <v>11.10497174463661</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.39972565629144</v>
+        <v>11.49963369231011</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.440091832598846</v>
+        <v>8.56378845362709</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.223533793656699</v>
+        <v>6.372223341434527</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.054059863044913</v>
+        <v>4.226058622611575</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.262166030534353</v>
+        <v>-3.291361824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-5.654602123598181</v>
+        <v>-5.655788910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.14312350835322</v>
+        <v>-2.143276898357541</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.237101635235142</v>
+        <v>4.236607142857139</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2074379178605525</v>
+        <v>-0.1588919980947807</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6913138882254657</v>
+        <v>-0.6673564792758526</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.7864757525083661</v>
+        <v>0.8344874314986868</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.663157108721627</v>
+        <v>2.712404671115344</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.727174952198851</v>
+        <v>5.800432061978547</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.658506155868992</v>
+        <v>5.757853481163565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.016304997608799</v>
+        <v>7.116213033627474</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.144433149964122</v>
+        <v>3.268129770992367</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.161782296650713</v>
+        <v>1.310471844428541</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.737482053122754</v>
+        <v>-1.565483293556092</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.015179046675101</v>
+        <v>-6.016365833119757</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.602258123737833</v>
+        <v>-1.602411513742155</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.297197789081295</v>
+        <v>4.296703296703292</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.971860994783626</v>
+        <v>-2.923315075017854</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.636025426687006</v>
+        <v>-3.612068017737393</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.8361204013377872</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.6198878779524009</v>
+        <v>0.6691354403461176</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.481982644506537</v>
+        <v>2.555239754286234</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.632063848176678</v>
+        <v>1.731411173471251</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4613360808051041</v>
+        <v>-0.3376394597768595</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.7661023187339</v>
+        <v>-3.617412770956072</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.386520514661221</v>
+        <v>-7.214521755094559</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-7.663530695026751</v>
+        <v>-7.664717481471406</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.105921127400833</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.788040078701655</v>
+        <v>-5.764082669752042</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.301321866539247</v>
+        <v>-2.253310187548927</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3874381293736064</v>
+        <v>-0.3381905669798897</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4484202858963826</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-2.488815272702439</v>
+        <v>-2.389467947407866</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.040090659559688</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.841193893825476</v>
+        <v>-7.692504346047649</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-11.18688681502751</v>
+        <v>-11.01488805546085</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.290439840058163</v>
+        <v>-1.319635634410794</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.465507444027736</v>
+        <v>1.465354054023415</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1330331559557862</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.216611507273079</v>
+        <v>-2.192654098323466</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-3.443786378025123</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.4826762246117</v>
+        <v>-13.43342866221798</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.92461076208686</v>
+        <v>-15.85135365230717</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-19.1554819393691</v>
+        <v>-19.05613461407453</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-15.78875452620073</v>
+        <v>-15.68884649018205</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.37342399289302</v>
+        <v>-13.24972737186478</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.79357484620643</v>
+        <v>-13.6448852984286</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-13.5678391959799</v>
+        <v>-13.39584043641324</v>
       </c>
     </row>
     <row r="7">
@@ -3963,826 +3963,826 @@
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1873380488829781</v>
+        <v>-0.2165338432356094</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.715955334607351</v>
+        <v>-2.717142121052007</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5589980512798078</v>
+        <v>0.5588446612754865</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.606654387528714</v>
+        <v>1.606159895150711</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7664975508880758</v>
+        <v>-0.717951631122304</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.303985906574091</v>
+        <v>-2.280028497624478</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.38869626584026</v>
+        <v>-2.340684586849939</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-10.1952144509114</v>
+        <v>-10.14596688851768</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.17362780009472</v>
+        <v>-11.10037069031502</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-15.69327136706679</v>
+        <v>-15.59392404177221</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.31081656202423</v>
+        <v>-11.21090852600555</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-10.35900721700835</v>
+        <v>-10.23531059598011</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.77915807032176</v>
+        <v>-10.63046852254394</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.718560034774129</v>
+        <v>-8.546561275207466</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1028</t>
+          <t>X &lt; -0.1027</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>136</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.930848675347995</v>
+        <v>1.901652880995364</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.886219770657</v>
+        <v>-1.887406557101656</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.395479432823251</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.260998694058671</v>
+        <v>2.260504201680668</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.722709140962976</v>
+        <v>1.771255060728748</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5494949353039473</v>
+        <v>0.5734523442535604</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.005803659256344</v>
+        <v>-0.9577919802660233</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.619931126572489</v>
+        <v>-6.570683564178772</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.475030930154091</v>
+        <v>-4.401773820374395</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.795537961778066</v>
+        <v>-6.696190636483493</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.794356767097085</v>
+        <v>-4.69444873107841</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.759978614741762</v>
+        <v>-4.636281993713517</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.444835350408106</v>
+        <v>-4.296145802630278</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.483805582534515</v>
+        <v>-4.047100940614911</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.09312</t>
+          <t>X &lt; -0.0931</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.306387837883889</v>
+        <v>-2.307574624328545</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.000494492378003</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7595789689173955</v>
+        <v>0.7835363778670086</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.706083771301159</v>
+        <v>-1.658072092310839</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.488815272702439</v>
+        <v>-2.389467947407866</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.063900183369213</v>
+        <v>-1.940203562340969</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.293574846206425</v>
+        <v>-1.144885298428598</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.73635929863174</v>
+        <v>-1.491078531651326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.08349</t>
+          <t>X &lt; -0.08346</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8248690934325893</v>
+        <v>0.795673299079958</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.04012928136049254</v>
+        <v>0.03894249491583679</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.124696739580664</v>
+        <v>2.124543349576342</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.494591304656623</v>
+        <v>3.49409681227862</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.956301751560929</v>
+        <v>3.004847671326701</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3611137977249399</v>
+        <v>0.385071206674553</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.202935404516424</v>
+        <v>-2.154923725526103</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.083227188799029</v>
+        <v>-3.033979626405312</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1615757786451368</v>
+        <v>0.2348328884248332</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.9645495442987411</v>
+        <v>1.063896869593314</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.58629466703028</v>
+        <v>1.686202703048956</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.44711910037735</v>
+        <v>2.570815721405594</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.02563084436855</v>
+        <v>0.9359883733541565</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>1.185033235369524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.07385</t>
+          <t>X &lt; -0.07383</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6893850859089454</v>
+        <v>-0.7185808802615767</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3052920132096375</v>
+        <v>0.3041052267649818</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.167849618682617</v>
+        <v>3.167696228678295</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.623807661293775</v>
+        <v>3.623313168915772</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.759785209175284</v>
+        <v>2.808331128941056</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.200169751417647</v>
+        <v>-0.176212342468034</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.23927750482062</v>
+        <v>-2.1912658258303</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.403414552516153</v>
+        <v>-1.354166990122437</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1642677860750723</v>
+        <v>0.2375248958547687</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2915476868136224</v>
+        <v>0.3908950121081958</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.064045225621832</v>
+        <v>1.163953261640508</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.075622075045558</v>
+        <v>2.199318696073803</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.192419551552682</v>
+        <v>1.152694971464378</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.9520671272051118</v>
+        <v>0.4245411364113352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06421</t>
+          <t>X &lt; -0.06419</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6290641786825049</v>
+        <v>-0.6582599730351362</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.01802804952410497</v>
+        <v>-0.01921483596876072</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.562509207696159</v>
+        <v>1.562355817691838</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7050800302968696</v>
+        <v>0.7045855379188666</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.401358378435745</v>
+        <v>1.449904298201517</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5234898141513895</v>
+        <v>-0.4995324052017764</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.571163136380527</v>
+        <v>-3.523151457390206</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.544404619673436</v>
+        <v>-3.495157057279719</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.358473195949301</v>
+        <v>-3.285216086169605</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.714564831785324</v>
+        <v>-3.615217506490751</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.190870928317125</v>
+        <v>-2.09096289229845</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.270170810431914</v>
+        <v>-2.279709735180468</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.812008025929934</v>
+        <v>-1.934126921003553</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.201101456107828</v>
+        <v>-1.685082058988186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.05458</t>
+          <t>X &lt; -0.05456</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3597039093222278</v>
+        <v>-0.4939827926289198</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.04931201781596428</v>
+        <v>0.140582057699099</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.1500698758360102</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7948667867502905</v>
+        <v>0.8847926267280997</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.670718647796008</v>
+        <v>1.806833808356835</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>1.071554811046724</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.146920712138098</v>
+        <v>-1.005230310436801</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.613989355924836</v>
+        <v>-1.471063070820144</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.079011916488021</v>
+        <v>-1.911261486408556</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.928930712817881</v>
+        <v>-2.735090067223538</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.609074557047066</v>
+        <v>-1.527940192178974</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.275191596486181</v>
+        <v>-2.276225067717306</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.772668922861477</v>
+        <v>-1.864931381377907</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.43516535251176</v>
+        <v>-1.817499422588355</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04494</t>
+          <t>X &lt; -0.04493</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.450805095510574</v>
+        <v>-1.402516888178127</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.318726529303412</v>
+        <v>-1.245187644220046</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.555019308670175</v>
+        <v>-1.480697784433488</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3154439273639085</v>
+        <v>-0.243218806509951</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.523445600364482</v>
+        <v>1.571991520130254</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.552990786893389</v>
+        <v>0.5769481958430021</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.433462837032053</v>
+        <v>-1.385451158041732</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.900531480818792</v>
+        <v>-1.851283918425075</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.436949453506379</v>
+        <v>-2.363692343726683</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.044370828257989</v>
+        <v>-3.02904231915339</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.846820996031902</v>
+        <v>-2.916225555912945</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.09043946150085</v>
+        <v>-2.224144396994951</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.78628389154705</v>
+        <v>-1.985387902005684</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.431371829480582</v>
+        <v>-2.845693277708229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03531</t>
+          <t>X &lt; -0.03529</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.849602899221225</v>
+        <v>-1.756342980665877</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.188061719557773</v>
+        <v>-1.078213533158412</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.456570478050189</v>
+        <v>-1.220695240066085</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4425069506234465</v>
+        <v>-0.2690925426774555</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7868802639576273</v>
+        <v>0.9470588835173146</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3266785360169564</v>
+        <v>0.4074780100053559</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.904496469713855</v>
+        <v>-1.856484790723535</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.119039860975342</v>
+        <v>-2.069792298581625</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.685072522548616</v>
+        <v>-2.611815412768919</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.089320961703699</v>
+        <v>-3.056856114796027</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.973805761884876</v>
+        <v>-3.008471309806865</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.618399549655649</v>
+        <v>-2.697779319916727</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.84361110436452</v>
+        <v>-2.966674620217923</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.566023984507765</v>
+        <v>-3.853993394566189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02567</t>
+          <t>X &lt; -0.02566</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.741999774376715</v>
+        <v>-1.531638243673669</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.481264685174537</v>
+        <v>-1.353562882645576</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.270124739880309</v>
+        <v>-1.989475478181241</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.450244423878154</v>
+        <v>-1.219887955182074</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1789537077552126</v>
+        <v>0.4038533404724447</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.311849602511181</v>
+        <v>-0.1531742592365575</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.381781636654196</v>
+        <v>-1.241932185020488</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.848850280440935</v>
+        <v>-1.753638635971264</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.448983824921463</v>
+        <v>-2.38116242621043</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.049385008987869</v>
+        <v>-3.008140613324628</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.201703895671827</v>
+        <v>-3.212281060860718</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.81810394202401</v>
+        <v>-2.858838732944633</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.185371168695816</v>
+        <v>-3.253996659508459</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.104863123489459</v>
+        <v>-3.300227388044284</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.01604</t>
+          <t>X &lt; -0.01602</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.599305927929777</v>
+        <v>-2.470896138612474</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.158400466139618</v>
+        <v>-2.05247258351222</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.316392056103815</v>
+        <v>-2.169666332764457</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.712607322933756</v>
+        <v>-1.526954177897579</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.04095212464824272</v>
+        <v>0.1496740915983708</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.138211086331232</v>
+        <v>-0.006677345417585911</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9332608299699245</v>
+        <v>-0.8123555551049364</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.120906872321022</v>
+        <v>-1.078013309957214</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.613487103137118</v>
+        <v>-1.624834315290585</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.26277548970063</v>
+        <v>-2.290809699578347</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.87064571498027</v>
+        <v>-1.942463959269134</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.268601715329062</v>
+        <v>-2.357856811485924</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.408053151406385</v>
+        <v>-2.516234943258908</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.774188402329102</v>
+        <v>-2.97752946561608</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0064</t>
+          <t>X &lt; -0.006388</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.415753123266185</v>
+        <v>-1.296670630114114</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5833301937736195</v>
+        <v>-0.5440983745509271</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9154449369246507</v>
+        <v>-0.8421670852734309</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.223816284564357</v>
+        <v>-1.052903455646607</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4308766184803048</v>
+        <v>0.5497402539326686</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7282506481153916</v>
+        <v>0.9195271037453736</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>0.01907909296026844</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5069338574013358</v>
+        <v>-0.412595328884656</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.035811551253758</v>
+        <v>-0.9782186572209497</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.412002638100866</v>
+        <v>-1.392686256007906</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.142380577501193</v>
+        <v>-1.186953059046289</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.51358571796041</v>
+        <v>-1.567108175156662</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.521705746143496</v>
+        <v>-1.586561655884545</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.513143262190766</v>
+        <v>-1.650603832065798</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.003235</t>
+          <t>X &lt; 0.003247</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.017476277702222</v>
+        <v>-1.972477416284832</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.593390119476595</v>
+        <v>-1.583043008403493</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.93664166909511</v>
+        <v>-1.898610701535404</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.630733887691186</v>
+        <v>-2.562271062271058</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.441329670437874</v>
+        <v>-1.434385841091192</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.013242072856713</v>
+        <v>-0.980177321164966</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.379900666480282</v>
+        <v>-1.372834730802289</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.871077532476107</v>
+        <v>-1.862685256942207</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.111151494082144</v>
+        <v>-2.129355855759236</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.365153404854524</v>
+        <v>-2.411513802787049</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.025027732484276</v>
+        <v>-2.073426055410096</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.014322670004837</v>
+        <v>-2.090392371129155</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.992332610181585</v>
+        <v>-2.097082251398355</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.359730887923376</v>
+        <v>-2.517795246157839</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.01287</t>
+          <t>X &lt; 0.01288</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2290</v>
+        <v>2302</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.286821371394097</v>
+        <v>-1.27901031300793</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.094708552790188</v>
+        <v>-1.111439298979747</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.336069510091598</v>
+        <v>-1.352569483744482</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.87838749519964</v>
+        <v>-1.891744933267425</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.349918344132853</v>
+        <v>-1.406322763996982</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.20330801355184</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.569518479098072</v>
+        <v>-1.624301546413832</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.83923836166165</v>
+        <v>-1.893856160773744</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.920564699217266</v>
+        <v>-1.994458488519932</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.049781769152801</v>
+        <v>-2.144764688827763</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.66398556061187</v>
+        <v>-1.761566250537378</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.518524965219122</v>
+        <v>-1.636384117896519</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.478303910245842</v>
+        <v>-1.61709545908861</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.883497336965547</v>
+        <v>-2.039256099811524</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.02251</t>
+          <t>X &lt; 0.02252</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2654</v>
+        <v>2665</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9623558505568539</v>
+        <v>-0.9417772468436638</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6037300305749298</v>
+        <v>-0.6005731834832559</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6407196621993734</v>
+        <v>-0.6379984977596322</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7530447611612558</v>
+        <v>-0.7496662216288428</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7830340500423105</v>
+        <v>-0.8074989539661388</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.7658584036274192</v>
+        <v>-0.776374904266504</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.243717314007981</v>
+        <v>-1.265999095447427</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.239568455188142</v>
+        <v>-1.262581289199147</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.317884280595429</v>
+        <v>-1.35429640244093</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.54557115790076</v>
+        <v>-1.595965833186376</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.278117753614389</v>
+        <v>-1.329954507601911</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.223036729553947</v>
+        <v>-1.288722497474069</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.43414519864119</v>
+        <v>-1.513280968774765</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.564394261110692</v>
+        <v>-1.656360404250279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.03214</t>
+          <t>X &lt; 0.03215</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2940</v>
+        <v>2952</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9401100704937164</v>
+        <v>-0.9080882161180099</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9416956195331423</v>
+        <v>-0.955637088180481</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.216795568671763</v>
+        <v>-1.230192608786169</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.271902602052997</v>
+        <v>-1.284894376386617</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.012265825625903</v>
+        <v>-1.046999900830336</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9679845123774271</v>
+        <v>-0.9925253981947719</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.543489042198118</v>
+        <v>-1.575796870630406</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.653076767721004</v>
+        <v>-1.685626092914404</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.594026236256155</v>
+        <v>-1.636898847727238</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.712417757174492</v>
+        <v>-1.766038602733587</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.524883840311688</v>
+        <v>-1.579588573817531</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.471899276956343</v>
+        <v>-1.536795753719886</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.737422905661425</v>
+        <v>-1.811882540942264</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.867158923871052</v>
+        <v>-1.950815271875875</v>
       </c>
     </row>
     <row r="23">
@@ -4792,101 +4792,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3150</v>
+        <v>3161</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.010792729870424</v>
+        <v>-0.9978244902934108</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.309053420245874</v>
+        <v>-1.30413038498768</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.592219917717344</v>
+        <v>-1.586648588143163</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.793357225524346</v>
+        <v>-1.786975717439297</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.428651118240417</v>
+        <v>-1.439451935003298</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.272674717864476</v>
+        <v>-1.276036267852689</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.6889261321923</v>
+        <v>-1.698656507895258</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.695603981265698</v>
+        <v>-1.705715789888764</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.517773542254403</v>
+        <v>-1.53630988369423</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.621435981099943</v>
+        <v>-1.648100310305637</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.650292290688064</v>
+        <v>-1.677047080152548</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.598587154604402</v>
+        <v>-1.633269217309874</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.684040458030339</v>
+        <v>-1.726569585046477</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.663077291217988</v>
+        <v>-1.713280667804753</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.05141</t>
+          <t>X &lt; 0.05142</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3303</v>
+        <v>3314</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.15401615116162</v>
+        <v>-1.142513387856624</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.331921128123064</v>
+        <v>-1.327203522189556</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.710772120302529</v>
+        <v>-1.705072011139499</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.77590583533533</v>
+        <v>-1.769898573147678</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.483102169068282</v>
+        <v>-1.490990252684014</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.471620064607229</v>
+        <v>-1.473064637012158</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.661126211237857</v>
+        <v>-1.668288464315829</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.628641773115788</v>
+        <v>-1.636239907197911</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.552525773315054</v>
+        <v>-1.56671542220343</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.509291319183923</v>
+        <v>-1.530516772000993</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.636995819088121</v>
+        <v>-1.657952251268512</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.525574414332397</v>
+        <v>-1.553191097523921</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.687037315940088</v>
+        <v>-1.720731021333144</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.626314175435809</v>
+        <v>-1.666381000254944</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3444</v>
+        <v>3455</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9622582347576625</v>
+        <v>-0.9530183992814472</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.227518790264845</v>
+        <v>-1.223372555846126</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.404384362188239</v>
+        <v>-1.399894757561228</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.664117965228087</v>
+        <v>-1.658730158730158</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.260417211228635</v>
+        <v>-1.266715323729883</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.382036657634501</v>
+        <v>-1.382731515371717</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.509280912226494</v>
+        <v>-1.514678513042043</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.555139992727646</v>
+        <v>-1.560655860522907</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.54259527105426</v>
+        <v>-1.553252909119713</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.419872614432627</v>
+        <v>-1.436467493106456</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.550700732011158</v>
+        <v>-1.567003420970558</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.645540732798501</v>
+        <v>-1.666604102308177</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.643460809299938</v>
+        <v>-1.669852229645528</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.605005281926466</v>
+        <v>-1.636485464323101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.07068</t>
+          <t>X &lt; 0.07069</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3553</v>
+        <v>3564</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6581454192051339</v>
+        <v>-0.651012020581696</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8522704265434839</v>
+        <v>-0.8494410353224779</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.14792850274155</v>
+        <v>-1.144369555700202</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.535991614835019</v>
+        <v>-1.531177552162447</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.161080534368132</v>
+        <v>-1.166011365573084</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.297928954218165</v>
+        <v>-1.298130555423661</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.395757393559045</v>
+        <v>-1.399874441926116</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.398289224518045</v>
+        <v>-1.402616337288016</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.47226996067355</v>
+        <v>-1.480581527262132</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.407446543034574</v>
+        <v>-1.420537774441812</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.456171099129115</v>
+        <v>-1.469214146075359</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.547022546238409</v>
+        <v>-1.563965013079425</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.614139200254186</v>
+        <v>-1.63526798726852</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.429203837530295</v>
+        <v>-1.455003495576292</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3660</v>
+        <v>3671</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5887298067390887</v>
+        <v>-0.5828588390020784</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5245639972365268</v>
+        <v>-0.522830044987181</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8775027646866462</v>
+        <v>-0.8748595979773128</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.304877247598647</v>
+        <v>-1.300908138316458</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8475135515482037</v>
+        <v>-0.8518267807034832</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9443468762298295</v>
+        <v>-0.9449030272508452</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.068966366389922</v>
+        <v>-1.072544243324593</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.057689863455131</v>
+        <v>-1.061476889939861</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.13119817194849</v>
+        <v>-1.138156077303286</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.092994935834071</v>
+        <v>-1.103753661693574</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.14618988363609</v>
+        <v>-1.156871479165119</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.20599011601076</v>
+        <v>-1.219856888414121</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.17407197813759</v>
+        <v>-1.191570639231585</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.015145987548983</v>
+        <v>-1.036421048936099</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3742</v>
+        <v>3753</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6034193594291608</v>
+        <v>-0.5982690208508714</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2295555066562471</v>
+        <v>-0.2287470773735123</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7432017790699845</v>
+        <v>-0.7410120205679576</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.025091861566558</v>
+        <v>-1.02203788770359</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6960576192735033</v>
+        <v>-0.6996615355748474</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6242305548921365</v>
+        <v>-0.6251885053327584</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7212179658165212</v>
+        <v>-0.724688100416202</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.853718558300784</v>
+        <v>-0.8569455550086218</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.9535863234883664</v>
+        <v>-0.9593138134871282</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9614718206392823</v>
+        <v>-0.9702124624084405</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.071353547117511</v>
+        <v>-1.079839948268159</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9688147132837344</v>
+        <v>-0.9803722263445209</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9734534767930541</v>
+        <v>-0.9879098817302179</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7328388142130819</v>
+        <v>-0.750718438773248</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3818</v>
+        <v>3829</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4318426815393082</v>
+        <v>-0.4278629961519513</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1234337162874795</v>
+        <v>-0.1229686809358341</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4779939053237072</v>
+        <v>-0.47661023169087</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.673262784827557</v>
+        <v>-0.6712871655565138</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3091004472569452</v>
+        <v>-0.3127807422323556</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3111028322923772</v>
+        <v>-0.312464962465846</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3031892801713738</v>
+        <v>-0.3068381680842123</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5991336862574528</v>
+        <v>-0.6020510003318478</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6458468892869007</v>
+        <v>-0.6508916208592126</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6442312852613128</v>
+        <v>-0.6517392008087768</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.7035736336395644</v>
+        <v>-0.7109659851616712</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5761165882557719</v>
+        <v>-0.5861184670655746</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6151062867480803</v>
+        <v>-0.627354526328638</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.322310497334378</v>
+        <v>-0.3376006871314345</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3875</v>
+        <v>3886</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3461423679829139</v>
+        <v>-0.3428894601780854</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.0658608063869579</v>
+        <v>-0.06558239388070319</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.343795793479309</v>
+        <v>-0.3428134007953076</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3798143879308782</v>
+        <v>-0.3787034320915197</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1833004307338797</v>
+        <v>-0.1865717156814313</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1808757604891724</v>
+        <v>-0.1822351387519632</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2258085081819985</v>
+        <v>-0.2289196453058366</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4727131566738834</v>
+        <v>-0.4752237975383053</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5711497900691924</v>
+        <v>-0.5752586345005071</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6078076492354114</v>
+        <v>-0.6138528170369568</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6692771323550986</v>
+        <v>-0.6751938190338791</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.465800277944048</v>
+        <v>-0.474154179624918</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5361666197579495</v>
+        <v>-0.5462782198884142</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2701433434453335</v>
+        <v>-0.2828340398247562</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3933</v>
+        <v>3944</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.30149383083846</v>
+        <v>-0.2988406598629751</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1250552287946292</v>
+        <v>-0.1246337027627575</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3540134677852649</v>
+        <v>-0.3530193130225214</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4636734725508092</v>
+        <v>-0.4623527711539879</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3033600386114443</v>
+        <v>-0.3055369512948829</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.29662504021735</v>
+        <v>-0.2972906898021677</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3167920139890938</v>
+        <v>-0.3188993693112323</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.6177358844238441</v>
+        <v>-0.6190826706568089</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7156577039718002</v>
+        <v>-0.7182277253093687</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.738933201509731</v>
+        <v>-0.7430647052599468</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.7263271162123388</v>
+        <v>-0.7305297456985897</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4999442325009369</v>
+        <v>-0.506262018161209</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4992179575434861</v>
+        <v>-0.5070978640632191</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2592052923803152</v>
+        <v>-0.2692104740834722</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3992</v>
+        <v>4003</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02149031268167079</v>
+        <v>-0.02007198424953316</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2036021721061161</v>
+        <v>0.2030996329210453</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.0222446530257443</v>
+        <v>0.0221908395597481</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1587473152895953</v>
+        <v>-0.1582891317503936</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.01633426409395611</v>
+        <v>0.0140267456739096</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.04756388822546853</v>
+        <v>-0.04855038353912988</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.01860833101251558</v>
+        <v>-0.0207962343367285</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2468916656655722</v>
+        <v>-0.2485113927409799</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3191566715189396</v>
+        <v>-0.3216986765444076</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.379563163450328</v>
+        <v>-0.3831575620108865</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3951077057704282</v>
+        <v>-0.3986864920839608</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2716284424244648</v>
+        <v>-0.2766579943010115</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1768885022473512</v>
+        <v>-0.1833468368901379</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1123568026217541</v>
+        <v>-0.1200829687996645</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4031</v>
+        <v>4042</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1155231386051128</v>
+        <v>0.1162753514385457</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2487338892635549</v>
+        <v>0.2481023085067449</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.06532837190408003</v>
+        <v>0.0651566693700687</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1126493546188527</v>
+        <v>-0.1123254830066287</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.03080465639687446</v>
+        <v>0.02894742427006491</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.06943289315606194</v>
+        <v>0.06836882936612199</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.04779014081941568</v>
+        <v>0.04590537420059349</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.03415834830091313</v>
+        <v>-0.03586607987280388</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1062616186633889</v>
+        <v>-0.1086518273221699</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.0998968800665736</v>
+        <v>-0.103259346320371</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1419901189008712</v>
+        <v>-0.1452594632822866</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.01930972134756104</v>
+        <v>-0.02378417559516777</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.04571086807928282</v>
+        <v>0.04014349914039173</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1118574407993549</v>
+        <v>0.1052552022380766</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4055</v>
+        <v>4066</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07562280919032105</v>
+        <v>0.07630641487765644</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2231179403310009</v>
+        <v>0.2225521885348982</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.03845851328966887</v>
+        <v>0.03835941510824625</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.08850568333804887</v>
+        <v>-0.08825178746671014</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1001408222969218</v>
+        <v>0.09839327797883612</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1403145267388481</v>
+        <v>0.1392064809597926</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.0936981798840435</v>
+        <v>0.09198344181049123</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.0341094603591543</v>
+        <v>0.0325176377165235</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.01134982904614645</v>
+        <v>0.009087797670019881</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.03731713147875126</v>
+        <v>0.03418947624955848</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.05498935921721682</v>
+        <v>-0.05788533206434465</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.09183886847533529</v>
+        <v>0.0878200364790942</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1786708568085018</v>
+        <v>0.1736541655497632</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2457947656195429</v>
+        <v>0.2398843896706637</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.06311528062025218</v>
+        <v>0.06368666254898159</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2264689554328925</v>
+        <v>0.2258911778048898</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.04078190035945539</v>
+        <v>0.04067629910401394</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.06044273440990366</v>
+        <v>-0.0602678571428612</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1246507207290719</v>
+        <v>0.1230829713801924</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1660902876256287</v>
+        <v>0.1650354357217054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1192936114010621</v>
+        <v>0.1177530679511634</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05771420257116944</v>
+        <v>0.0563074081632351</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.08379259925767713</v>
+        <v>0.08170497813596711</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1299988624147161</v>
+        <v>0.1271230410657651</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.06168569893297615</v>
+        <v>0.05897868537606854</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1834630739278182</v>
+        <v>0.1798225302878649</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2432960356104843</v>
+        <v>0.2388575796866803</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2866743885950385</v>
+        <v>0.2815247828022009</v>
       </c>
     </row>
   </sheetData>
